--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_step2_Central_African_Republic___CAR_1010_09AM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_step2_Central_African_Republic___CAR_1010_09AM.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN TOTAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall PiN and severity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN total par admin" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- hote" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- idp_host" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- retourne" sheetId="5" state="visible" r:id="rId5"/>
@@ -191,56 +191,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,22 +587,22 @@
   <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="33" customWidth="1" min="19" max="19"/>
-    <col width="33" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="37" customWidth="1" min="19" max="19"/>
+    <col width="37" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,12 +644,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Population group</t>
+          <t>Groupe de population</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="F5" s="7" t="n"/>
@@ -683,62 +661,62 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Population group</t>
+          <t>Groupe de population</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>TotN</t>
+          <t>Population totale</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>% severity levels 1-2</t>
+          <t>% niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t># severity levels 1-2</t>
+          <t># niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>% severity level 3</t>
+          <t>% niveau de sévérité 3</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t># severity level 3</t>
+          <t># niveau de sévérité 3</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>% severity level 4</t>
+          <t>% niveau de sévérité 4</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t># severity level 4</t>
+          <t># niveau de sévérité 4</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>% severity level 5</t>
+          <t>% niveau de sévérité 5</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t># severity level 5</t>
+          <t># niveau de sévérité 5</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
     </row>
@@ -747,12 +725,12 @@
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>TOTAL (5-17 y.o.)</t>
+          <t>TOTAL (5-17 ans)</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>All population groups</t>
+          <t>Tous les groupes de population</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
@@ -762,12 +740,12 @@
       <c r="G6" s="10" t="n"/>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>TOTAL (5-17 y.o.)</t>
+          <t>TOTAL (5-17 ans)</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>All population groups</t>
+          <t>Tous les groupes de population</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
@@ -809,7 +787,7 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>hote (5-17 y.o.)</t>
+          <t>hote (5-17 ans)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -824,7 +802,7 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>hote (5-17 y.o.)</t>
+          <t>hote (5-17 ans)</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -871,7 +849,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>idp_host (5-17 y.o.)</t>
+          <t>idp_host (5-17 ans)</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -886,7 +864,7 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>idp_host (5-17 y.o.)</t>
+          <t>idp_host (5-17 ans)</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -933,7 +911,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>retourne (5-17 y.o.)</t>
+          <t>retourne (5-17 ans)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -948,7 +926,7 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>retourne (5-17 y.o.)</t>
+          <t>retourne (5-17 ans)</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -995,7 +973,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>idp_site (5-17 y.o.)</t>
+          <t>idp_site (5-17 ans)</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1010,7 +988,7 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>idp_site (5-17 y.o.)</t>
+          <t>idp_site (5-17 ans)</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1057,12 +1035,12 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Girls (5-17 y.o.)</t>
+          <t>Filles (5-17 ans)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>All population groups</t>
+          <t>Tous les groupes de population</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -1089,12 +1067,12 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Boys (5-17 y.o.)</t>
+          <t>Garcons (5-17 ans)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>All population groups</t>
+          <t>Tous les groupes de population</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -1121,12 +1099,12 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>ECE (5 y.o.)</t>
+          <t>Éducation préscolaire (5 ans)</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>All population groups</t>
+          <t>Tous les groupes de population</t>
         </is>
       </c>
       <c r="E13" s="13" t="n">
@@ -1153,12 +1131,12 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Children with disability</t>
+          <t>Enfants en situation de handicap</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>All population groups</t>
+          <t>Tous les groupes de population</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
@@ -1197,25 +1175,25 @@
   <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="33" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="37" customWidth="1" min="15" max="15"/>
+    <col width="37" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Overall PiN and severity (5-17 y.o.)</t>
+          <t>PiN total par admin (5-17 ans)</t>
         </is>
       </c>
     </row>
@@ -1234,62 +1212,62 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>TotN</t>
+          <t>Population totale</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>% severity levels 1-2</t>
+          <t>% niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t># severity levels 1-2</t>
+          <t># niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>% severity level 3</t>
+          <t>% niveau de sévérité 3</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t># severity level 3</t>
+          <t># niveau de sévérité 3</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
         <is>
-          <t>% severity level 4</t>
+          <t>% niveau de sévérité 4</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t># severity level 4</t>
+          <t># niveau de sévérité 4</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>% severity level 5</t>
+          <t>% niveau de sévérité 5</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t># severity level 5</t>
+          <t># niveau de sévérité 5</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
         <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t>Area severity</t>
+          <t>Sévérité de la zone</t>
         </is>
       </c>
     </row>
@@ -4377,26 +4355,26 @@
   <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="37" customWidth="1" min="16" max="16"/>
+    <col width="37" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>PiN -- hote (5-17 y.o.)</t>
+          <t>PiN -- hote (5-17 ans)</t>
         </is>
       </c>
     </row>
@@ -4415,67 +4393,67 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Population group</t>
+          <t>Groupe de population</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>TotN</t>
+          <t>Population totale</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>% severity levels 1-2</t>
+          <t>% niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t># severity levels 1-2</t>
+          <t># niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>% severity level 3</t>
+          <t>% niveau de sévérité 3</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t># severity level 3</t>
+          <t># niveau de sévérité 3</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>% severity level 4</t>
+          <t>% niveau de sévérité 4</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t># severity level 4</t>
+          <t># niveau de sévérité 4</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>% severity level 5</t>
+          <t>% niveau de sévérité 5</t>
         </is>
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t># severity level 5</t>
+          <t># niveau de sévérité 5</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
         <is>
-          <t>Area severity</t>
+          <t>Sévérité de la zone</t>
         </is>
       </c>
     </row>
@@ -7790,26 +7768,26 @@
   <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="37" customWidth="1" min="16" max="16"/>
+    <col width="37" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>PiN -- idp_host (5-17 y.o.)</t>
+          <t>PiN -- idp_host (5-17 ans)</t>
         </is>
       </c>
     </row>
@@ -7828,67 +7806,67 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Population group</t>
+          <t>Groupe de population</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>TotN</t>
+          <t>Population totale</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>% severity levels 1-2</t>
+          <t>% niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t># severity levels 1-2</t>
+          <t># niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>% severity level 3</t>
+          <t>% niveau de sévérité 3</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t># severity level 3</t>
+          <t># niveau de sévérité 3</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>% severity level 4</t>
+          <t>% niveau de sévérité 4</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t># severity level 4</t>
+          <t># niveau de sévérité 4</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>% severity level 5</t>
+          <t>% niveau de sévérité 5</t>
         </is>
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t># severity level 5</t>
+          <t># niveau de sévérité 5</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
         <is>
-          <t>Area severity</t>
+          <t>Sévérité de la zone</t>
         </is>
       </c>
     </row>
@@ -10879,26 +10857,26 @@
   <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="37" customWidth="1" min="16" max="16"/>
+    <col width="37" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>PiN -- retourne (5-17 y.o.)</t>
+          <t>PiN -- retourne (5-17 ans)</t>
         </is>
       </c>
     </row>
@@ -10917,67 +10895,67 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Population group</t>
+          <t>Groupe de population</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>TotN</t>
+          <t>Population totale</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>% severity levels 1-2</t>
+          <t>% niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t># severity levels 1-2</t>
+          <t># niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>% severity level 3</t>
+          <t>% niveau de sévérité 3</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t># severity level 3</t>
+          <t># niveau de sévérité 3</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>% severity level 4</t>
+          <t>% niveau de sévérité 4</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t># severity level 4</t>
+          <t># niveau de sévérité 4</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>% severity level 5</t>
+          <t>% niveau de sévérité 5</t>
         </is>
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t># severity level 5</t>
+          <t># niveau de sévérité 5</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
         <is>
-          <t>Area severity</t>
+          <t>Sévérité de la zone</t>
         </is>
       </c>
     </row>
@@ -13968,26 +13946,26 @@
   <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="37" customWidth="1" min="16" max="16"/>
+    <col width="37" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>PiN -- idp_site (5-17 y.o.)</t>
+          <t>PiN -- idp_site (5-17 ans)</t>
         </is>
       </c>
     </row>
@@ -14006,67 +13984,67 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Population group</t>
+          <t>Groupe de population</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>TotN</t>
+          <t>Population totale</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>% severity levels 1-2</t>
+          <t>% niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t># severity levels 1-2</t>
+          <t># niveaux de sévérité 1-2</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>% severity level 3</t>
+          <t>% niveau de sévérité 3</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t># severity level 3</t>
+          <t># niveau de sévérité 3</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>% severity level 4</t>
+          <t>% niveau de sévérité 4</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t># severity level 4</t>
+          <t># niveau de sévérité 4</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>% severity level 5</t>
+          <t>% niveau de sévérité 5</t>
         </is>
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t># severity level 5</t>
+          <t># niveau de sévérité 5</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t># Tot PiN (severity levels 3-5)</t>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
         <is>
-          <t>Area severity</t>
+          <t>Sévérité de la zone</t>
         </is>
       </c>
     </row>

--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_step2_Central_African_Republic___CAR_1010_09AM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_step2_Central_African_Republic___CAR_1010_09AM.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>715712</v>
+        <v>128737</v>
       </c>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
@@ -749,37 +749,37 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1738001</v>
+        <v>325638</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>58.8</v>
+        <v>60.5</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1022273</v>
+        <v>196911</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>35.6</v>
+        <v>34.2</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>617873</v>
+        <v>111509</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>60364</v>
+        <v>10092</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>37475</v>
+        <v>7136</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>715712</v>
+        <v>128737</v>
       </c>
     </row>
     <row r="7">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>655151</v>
+        <v>68175</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -811,37 +811,37 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1582055</v>
+        <v>169692</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>58.6</v>
+        <v>59.8</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>926885</v>
+        <v>101524</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>564913</v>
+        <v>58549</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>55702</v>
+        <v>5430</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>34536</v>
+        <v>4197</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>41.4</v>
+        <v>40.2</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>655151</v>
+        <v>68175</v>
       </c>
     </row>
     <row r="8">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>359771</v>
+        <v>64713</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>355941</v>
+        <v>64024</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E13" s="13" t="n">
-        <v>55055</v>
+        <v>9903</v>
       </c>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>71571</v>
+        <v>12874</v>
       </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
@@ -1282,37 +1282,37 @@
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>3963</v>
+        <v>1706</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>32.8</v>
+        <v>35</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>1299</v>
+        <v>597</v>
       </c>
       <c r="I6" s="24" t="n">
-        <v>58.9</v>
+        <v>56.3</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>2336</v>
+        <v>961</v>
       </c>
       <c r="K6" s="25" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>279</v>
+        <v>107</v>
       </c>
       <c r="O6" s="27" t="n">
-        <v>67.2</v>
+        <v>65</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>2664</v>
+        <v>1109</v>
       </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
@@ -1331,37 +1331,37 @@
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>19945</v>
+        <v>2134</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>62.8</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>12525</v>
+        <v>1340</v>
       </c>
       <c r="I7" s="24" t="n">
         <v>30.7</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>6123</v>
+        <v>655</v>
       </c>
       <c r="K7" s="25" t="n">
         <v>3.7</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>738</v>
+        <v>79</v>
       </c>
       <c r="M7" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>558</v>
+        <v>60</v>
       </c>
       <c r="O7" s="27" t="n">
         <v>37.2</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>7420</v>
+        <v>794</v>
       </c>
       <c r="Q7" s="28" t="inlineStr">
         <is>
@@ -1380,37 +1380,37 @@
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>29597</v>
+        <v>5891</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>65.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>19419</v>
+        <v>3820</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>9352</v>
+        <v>1885</v>
       </c>
       <c r="K8" s="25" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="M8" s="26" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>310</v>
+        <v>97</v>
       </c>
       <c r="O8" s="27" t="n">
-        <v>34.4</v>
+        <v>35.1</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>10178</v>
+        <v>2070</v>
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>48223</v>
+        <v>2158</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>56</v>
+        <v>53.8</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>27004</v>
+        <v>1161</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>43</v>
+        <v>44.7</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>20728</v>
+        <v>965</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>492</v>
+        <v>32</v>
       </c>
       <c r="M9" s="26" t="n">
         <v>0</v>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="27" t="n">
-        <v>44</v>
+        <v>46.2</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>21220</v>
+        <v>997</v>
       </c>
       <c r="Q9" s="28" t="inlineStr">
         <is>
@@ -1478,37 +1478,37 @@
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>11453</v>
+        <v>115</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>59.1</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>6769</v>
+        <v>68</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>39</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>4467</v>
+        <v>45</v>
       </c>
       <c r="K10" s="25" t="n">
         <v>1.6</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="M10" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O10" s="27" t="n">
         <v>40.9</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>4684</v>
+        <v>47</v>
       </c>
       <c r="Q10" s="28" t="inlineStr">
         <is>
@@ -1527,37 +1527,37 @@
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>23962</v>
+        <v>1295</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>43.9</v>
+        <v>46.2</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>10526</v>
+        <v>598</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>12467</v>
+        <v>658</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="O11" s="27" t="n">
-        <v>56.1</v>
+        <v>53.9</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>13437</v>
+        <v>698</v>
       </c>
       <c r="Q11" s="28" t="inlineStr">
         <is>
@@ -1576,37 +1576,37 @@
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>13437</v>
+        <v>556</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>3086</v>
+        <v>97</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>73.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>9923</v>
+        <v>404</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>295</v>
+        <v>51</v>
       </c>
       <c r="M12" s="26" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="O12" s="27" t="n">
-        <v>77</v>
+        <v>82.5</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>10351</v>
+        <v>458</v>
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
@@ -1625,41 +1625,31 @@
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>6728</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>27.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="23" t="inlineStr"/>
       <c r="H13" s="23" t="n">
-        <v>1870</v>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I13" s="24" t="inlineStr"/>
       <c r="J13" s="24" t="n">
-        <v>4440</v>
-      </c>
-      <c r="K13" s="25" t="n">
-        <v>6.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="25" t="inlineStr"/>
       <c r="L13" s="25" t="n">
-        <v>410</v>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M13" s="26" t="inlineStr"/>
       <c r="N13" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="27" t="n">
-        <v>72.09999999999999</v>
-      </c>
+      <c r="O13" s="27" t="inlineStr"/>
       <c r="P13" s="27" t="n">
-        <v>4851</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1674,37 +1664,37 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>64671</v>
+        <v>12131</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>76.5</v>
+        <v>70.3</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>49459</v>
+        <v>8530</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>21.7</v>
+        <v>25.9</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>14021</v>
+        <v>3145</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>1114</v>
+        <v>431</v>
       </c>
       <c r="M14" s="26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N14" s="26" t="n">
         <v>25</v>
       </c>
       <c r="O14" s="27" t="n">
-        <v>23.4</v>
+        <v>29.7</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>15159</v>
+        <v>3600</v>
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
@@ -1723,25 +1713,25 @@
         </is>
       </c>
       <c r="F15" s="22" t="n">
-        <v>20880</v>
+        <v>3453</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>60.3</v>
+        <v>57.3</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>12588</v>
+        <v>1979</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>28.7</v>
+        <v>30.7</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>5984</v>
+        <v>1062</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>2308</v>
+        <v>413</v>
       </c>
       <c r="M15" s="26" t="n">
         <v>0</v>
@@ -1750,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="27" t="n">
-        <v>39.7</v>
+        <v>42.7</v>
       </c>
       <c r="P15" s="27" t="n">
-        <v>8292</v>
+        <v>1475</v>
       </c>
       <c r="Q15" s="28" t="inlineStr">
         <is>
@@ -1772,37 +1762,37 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>25717</v>
+        <v>6561</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>14937</v>
+        <v>3826</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>7964</v>
+        <v>2007</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>2250</v>
+        <v>583</v>
       </c>
       <c r="M16" s="26" t="n">
         <v>2.3</v>
       </c>
       <c r="N16" s="26" t="n">
-        <v>589</v>
+        <v>149</v>
       </c>
       <c r="O16" s="27" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="P16" s="27" t="n">
-        <v>10803</v>
+        <v>2739</v>
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
@@ -1821,37 +1811,37 @@
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>35945</v>
+        <v>5670</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>67.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>24420</v>
+        <v>3560</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>28.4</v>
+        <v>30.7</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>10220</v>
+        <v>1743</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>698</v>
+        <v>183</v>
       </c>
       <c r="M17" s="26" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="N17" s="26" t="n">
-        <v>609</v>
+        <v>185</v>
       </c>
       <c r="O17" s="27" t="n">
-        <v>32.1</v>
+        <v>37.2</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>11526</v>
+        <v>2111</v>
       </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
@@ -1870,37 +1860,37 @@
         </is>
       </c>
       <c r="F18" s="22" t="n">
-        <v>14656</v>
+        <v>727</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>44.4</v>
+        <v>40.4</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>6506</v>
+        <v>294</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>41</v>
+        <v>46.5</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>6007</v>
+        <v>338</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="L18" s="25" t="n">
-        <v>1453</v>
+        <v>74</v>
       </c>
       <c r="M18" s="26" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="N18" s="26" t="n">
-        <v>690</v>
+        <v>21</v>
       </c>
       <c r="O18" s="27" t="n">
-        <v>55.6</v>
+        <v>59.6</v>
       </c>
       <c r="P18" s="27" t="n">
-        <v>8149</v>
+        <v>433</v>
       </c>
       <c r="Q18" s="28" t="inlineStr">
         <is>
@@ -1919,37 +1909,37 @@
         </is>
       </c>
       <c r="F19" s="22" t="n">
-        <v>8482</v>
+        <v>2160</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>47.2</v>
+        <v>39.9</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>4004</v>
+        <v>862</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>44.8</v>
+        <v>50.7</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>3802</v>
+        <v>1096</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>1.7</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="M19" s="26" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="N19" s="26" t="n">
-        <v>532</v>
+        <v>165</v>
       </c>
       <c r="O19" s="27" t="n">
-        <v>52.8</v>
+        <v>60.1</v>
       </c>
       <c r="P19" s="27" t="n">
-        <v>4478</v>
+        <v>1298</v>
       </c>
       <c r="Q19" s="28" t="inlineStr">
         <is>
@@ -1968,37 +1958,37 @@
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>61935</v>
+        <v>12099</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>36.9</v>
+        <v>37.5</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>22876</v>
+        <v>4537</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>61.4</v>
+        <v>60.8</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>38009</v>
+        <v>7360</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>825</v>
+        <v>177</v>
       </c>
       <c r="M20" s="26" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="O20" s="27" t="n">
-        <v>63.1</v>
+        <v>62.5</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>39058</v>
+        <v>7562</v>
       </c>
       <c r="Q20" s="28" t="inlineStr">
         <is>
@@ -2017,37 +2007,37 @@
         </is>
       </c>
       <c r="F21" s="22" t="n">
-        <v>20294</v>
+        <v>5108</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>49.6</v>
+        <v>56.5</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>10071</v>
+        <v>2888</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>43.4</v>
+        <v>37.7</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>8806</v>
+        <v>1927</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>243</v>
+        <v>46</v>
       </c>
       <c r="M21" s="26" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="N21" s="26" t="n">
-        <v>1174</v>
+        <v>248</v>
       </c>
       <c r="O21" s="27" t="n">
-        <v>50.4</v>
+        <v>43.5</v>
       </c>
       <c r="P21" s="27" t="n">
-        <v>10224</v>
+        <v>2221</v>
       </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
@@ -2066,37 +2056,37 @@
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>13748</v>
+        <v>4659</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>8397</v>
+        <v>2771</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>37.3</v>
+        <v>39.4</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>5124</v>
+        <v>1834</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="M22" s="26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="N22" s="26" t="n">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="O22" s="27" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>5340</v>
+        <v>1886</v>
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
@@ -2115,37 +2105,37 @@
         </is>
       </c>
       <c r="F23" s="22" t="n">
-        <v>13839</v>
+        <v>5046</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>7769</v>
+        <v>2836</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>4850</v>
+        <v>1816</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>661</v>
+        <v>247</v>
       </c>
       <c r="M23" s="26" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>560</v>
+        <v>147</v>
       </c>
       <c r="O23" s="27" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>6070</v>
+        <v>2210</v>
       </c>
       <c r="Q23" s="28" t="inlineStr">
         <is>
@@ -2164,37 +2154,37 @@
         </is>
       </c>
       <c r="F24" s="22" t="n">
-        <v>31209</v>
+        <v>20269</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>22563</v>
+        <v>14861</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>7471</v>
+        <v>4790</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>864</v>
+        <v>460</v>
       </c>
       <c r="M24" s="26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>322</v>
+        <v>169</v>
       </c>
       <c r="O24" s="27" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="P24" s="27" t="n">
-        <v>8657</v>
+        <v>5419</v>
       </c>
       <c r="Q24" s="28" t="inlineStr">
         <is>
@@ -2213,37 +2203,37 @@
         </is>
       </c>
       <c r="F25" s="22" t="n">
-        <v>16125</v>
+        <v>10200</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>56</v>
+        <v>58.5</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>9032</v>
+        <v>5969</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>37.4</v>
+        <v>35.7</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>6029</v>
+        <v>3641</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>759</v>
+        <v>357</v>
       </c>
       <c r="M25" s="26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="N25" s="26" t="n">
-        <v>294</v>
+        <v>229</v>
       </c>
       <c r="O25" s="27" t="n">
-        <v>43.9</v>
+        <v>41.4</v>
       </c>
       <c r="P25" s="27" t="n">
-        <v>7082</v>
+        <v>4226</v>
       </c>
       <c r="Q25" s="28" t="inlineStr">
         <is>
@@ -2262,37 +2252,37 @@
         </is>
       </c>
       <c r="F26" s="22" t="n">
-        <v>28483</v>
+        <v>9179</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>33.1</v>
+        <v>28.2</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>9418</v>
+        <v>2584</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>56.7</v>
+        <v>63.8</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>16146</v>
+        <v>5857</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>1207</v>
+        <v>396</v>
       </c>
       <c r="M26" s="26" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>1712</v>
+        <v>341</v>
       </c>
       <c r="O26" s="27" t="n">
-        <v>66.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="P26" s="27" t="n">
-        <v>19065</v>
+        <v>6594</v>
       </c>
       <c r="Q26" s="28" t="inlineStr">
         <is>
@@ -2311,37 +2301,37 @@
         </is>
       </c>
       <c r="F27" s="22" t="n">
-        <v>1985</v>
+        <v>1812</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>813</v>
+        <v>745</v>
       </c>
       <c r="I27" s="24" t="n">
         <v>52.3</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>1037</v>
+        <v>947</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="M27" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N27" s="26" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O27" s="27" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="P27" s="27" t="n">
-        <v>1172</v>
+        <v>1066</v>
       </c>
       <c r="Q27" s="28" t="inlineStr">
         <is>
@@ -2360,37 +2350,37 @@
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>76863</v>
+        <v>4386</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>47</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>36125</v>
+        <v>2062</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>35188</v>
+        <v>1994</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>3454</v>
+        <v>192</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>2019</v>
+        <v>135</v>
       </c>
       <c r="O28" s="27" t="n">
         <v>52.9</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>40661</v>
+        <v>2321</v>
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
@@ -2409,37 +2399,37 @@
         </is>
       </c>
       <c r="F29" s="22" t="n">
-        <v>20952</v>
+        <v>297</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>62</v>
+        <v>62.8</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>12993</v>
+        <v>187</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>31.2</v>
+        <v>30.7</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>6535</v>
+        <v>91</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>441</v>
+        <v>7</v>
       </c>
       <c r="M29" s="26" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>1004</v>
+        <v>13</v>
       </c>
       <c r="O29" s="27" t="n">
-        <v>38.1</v>
+        <v>37.2</v>
       </c>
       <c r="P29" s="27" t="n">
-        <v>7980</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
@@ -2458,37 +2448,37 @@
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>11142</v>
+        <v>446</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>45.8</v>
+        <v>52.7</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>5102</v>
+        <v>235</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>42.8</v>
+        <v>37.4</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>4766</v>
+        <v>167</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>632</v>
+        <v>22</v>
       </c>
       <c r="M30" s="26" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>632</v>
+        <v>22</v>
       </c>
       <c r="O30" s="27" t="n">
-        <v>54.1</v>
+        <v>47.2</v>
       </c>
       <c r="P30" s="27" t="n">
-        <v>6029</v>
+        <v>211</v>
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
@@ -2507,37 +2497,37 @@
         </is>
       </c>
       <c r="F31" s="22" t="n">
-        <v>15602</v>
+        <v>255</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>7226</v>
+        <v>120</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>44.2</v>
+        <v>45.9</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>6900</v>
+        <v>117</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>1057</v>
+        <v>14</v>
       </c>
       <c r="M31" s="26" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="N31" s="26" t="n">
-        <v>419</v>
+        <v>4</v>
       </c>
       <c r="O31" s="27" t="n">
-        <v>53.7</v>
+        <v>52.8</v>
       </c>
       <c r="P31" s="27" t="n">
-        <v>8376</v>
+        <v>135</v>
       </c>
       <c r="Q31" s="28" t="inlineStr">
         <is>
@@ -2556,37 +2546,37 @@
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>28500</v>
+        <v>1288</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>12259</v>
+        <v>558</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>14104</v>
+        <v>634</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>381</v>
+        <v>27</v>
       </c>
       <c r="M32" s="26" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="N32" s="26" t="n">
-        <v>1756</v>
+        <v>69</v>
       </c>
       <c r="O32" s="27" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>16241</v>
+        <v>730</v>
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
@@ -2605,37 +2595,37 @@
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>21928</v>
+        <v>1279</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>74.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>16394</v>
+        <v>907</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>22.6</v>
+        <v>26.8</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>4948</v>
+        <v>343</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="M33" s="26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N33" s="26" t="n">
-        <v>298</v>
+        <v>9</v>
       </c>
       <c r="O33" s="27" t="n">
-        <v>25.3</v>
+        <v>29.2</v>
       </c>
       <c r="P33" s="27" t="n">
-        <v>5556</v>
+        <v>373</v>
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
@@ -2654,37 +2644,37 @@
         </is>
       </c>
       <c r="F34" s="22" t="n">
-        <v>20108</v>
+        <v>5053</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>53.5</v>
+        <v>57.9</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>10757</v>
+        <v>2928</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>6264</v>
+        <v>1476</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="M34" s="26" t="n">
-        <v>13</v>
+        <v>11.3</v>
       </c>
       <c r="N34" s="26" t="n">
-        <v>2618</v>
+        <v>570</v>
       </c>
       <c r="O34" s="27" t="n">
-        <v>46.5</v>
+        <v>42</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>9351</v>
+        <v>2125</v>
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
@@ -2703,37 +2693,37 @@
         </is>
       </c>
       <c r="F35" s="22" t="n">
-        <v>7045</v>
+        <v>1368</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>47.1</v>
+        <v>43.8</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>3318</v>
+        <v>599</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>36.5</v>
+        <v>44.6</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>2568</v>
+        <v>610</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>256</v>
+        <v>52</v>
       </c>
       <c r="M35" s="26" t="n">
-        <v>12.7</v>
+        <v>7.8</v>
       </c>
       <c r="N35" s="26" t="n">
-        <v>896</v>
+        <v>107</v>
       </c>
       <c r="O35" s="27" t="n">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
       <c r="P35" s="27" t="n">
-        <v>3720</v>
+        <v>769</v>
       </c>
       <c r="Q35" s="28" t="inlineStr">
         <is>
@@ -2752,37 +2742,37 @@
         </is>
       </c>
       <c r="F36" s="22" t="n">
-        <v>16705</v>
+        <v>3024</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>3319</v>
+        <v>624</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>57</v>
+        <v>55.5</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>9519</v>
+        <v>1679</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>6.8</v>
+        <v>11.3</v>
       </c>
       <c r="L36" s="25" t="n">
-        <v>1135</v>
+        <v>342</v>
       </c>
       <c r="M36" s="26" t="n">
-        <v>16.4</v>
+        <v>12.5</v>
       </c>
       <c r="N36" s="26" t="n">
-        <v>2732</v>
+        <v>379</v>
       </c>
       <c r="O36" s="27" t="n">
-        <v>80.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>13386</v>
+        <v>2400</v>
       </c>
       <c r="Q36" s="28" t="inlineStr">
         <is>
@@ -2801,37 +2791,37 @@
         </is>
       </c>
       <c r="F37" s="22" t="n">
-        <v>52957</v>
+        <v>10362</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>68.2</v>
+        <v>66</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>36107</v>
+        <v>6844</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>30.3</v>
+        <v>31.3</v>
       </c>
       <c r="J37" s="24" t="n">
-        <v>16066</v>
+        <v>3245</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="L37" s="25" t="n">
-        <v>626</v>
+        <v>243</v>
       </c>
       <c r="M37" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="N37" s="26" t="n">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="O37" s="27" t="n">
-        <v>31.8</v>
+        <v>34</v>
       </c>
       <c r="P37" s="27" t="n">
-        <v>16850</v>
+        <v>3518</v>
       </c>
       <c r="Q37" s="28" t="inlineStr">
         <is>
@@ -2850,41 +2840,41 @@
         </is>
       </c>
       <c r="F38" s="22" t="n">
-        <v>12375</v>
+        <v>2077</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>80.7</v>
+        <v>76</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>9992</v>
+        <v>1579</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>18.2</v>
+        <v>22.9</v>
       </c>
       <c r="J38" s="24" t="n">
-        <v>2247</v>
+        <v>476</v>
       </c>
       <c r="K38" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" s="26" t="n">
         <v>0.4</v>
       </c>
-      <c r="L38" s="25" t="n">
-        <v>54</v>
-      </c>
-      <c r="M38" s="26" t="n">
-        <v>0.7</v>
-      </c>
       <c r="N38" s="26" t="n">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="O38" s="27" t="n">
-        <v>19.3</v>
+        <v>24</v>
       </c>
       <c r="P38" s="27" t="n">
-        <v>2382</v>
+        <v>498</v>
       </c>
       <c r="Q38" s="28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2899,25 +2889,25 @@
         </is>
       </c>
       <c r="F39" s="22" t="n">
-        <v>11670</v>
+        <v>360</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>50.5</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>5893</v>
+        <v>182</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>48.6</v>
       </c>
       <c r="J39" s="24" t="n">
-        <v>5672</v>
+        <v>175</v>
       </c>
       <c r="K39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="25" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="M39" s="26" t="n">
         <v>0</v>
@@ -2929,7 +2919,7 @@
         <v>49.6</v>
       </c>
       <c r="P39" s="27" t="n">
-        <v>5788</v>
+        <v>178</v>
       </c>
       <c r="Q39" s="28" t="inlineStr">
         <is>
@@ -2948,37 +2938,37 @@
         </is>
       </c>
       <c r="F40" s="22" t="n">
-        <v>74369</v>
+        <v>21627</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>48944</v>
+        <v>14345</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>22641</v>
+        <v>6555</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="L40" s="25" t="n">
-        <v>1445</v>
+        <v>390</v>
       </c>
       <c r="M40" s="26" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="N40" s="26" t="n">
-        <v>1398</v>
+        <v>343</v>
       </c>
       <c r="O40" s="27" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="P40" s="27" t="n">
-        <v>25484</v>
+        <v>7288</v>
       </c>
       <c r="Q40" s="28" t="inlineStr">
         <is>
@@ -2997,41 +2987,41 @@
         </is>
       </c>
       <c r="F41" s="22" t="n">
-        <v>35440</v>
+        <v>4670</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>42.5</v>
+        <v>36.5</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>15057</v>
+        <v>1703</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>14321</v>
+        <v>1890</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>3793</v>
+        <v>470</v>
       </c>
       <c r="M41" s="26" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="N41" s="26" t="n">
-        <v>2268</v>
+        <v>606</v>
       </c>
       <c r="O41" s="27" t="n">
-        <v>57.5</v>
+        <v>63.5</v>
       </c>
       <c r="P41" s="27" t="n">
-        <v>20382</v>
+        <v>2966</v>
       </c>
       <c r="Q41" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3046,37 +3036,37 @@
         </is>
       </c>
       <c r="F42" s="22" t="n">
-        <v>20180</v>
+        <v>12568</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>15589</v>
+        <v>9781</v>
       </c>
       <c r="I42" s="24" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="J42" s="24" t="n">
-        <v>3885</v>
+        <v>2378</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>435</v>
+        <v>260</v>
       </c>
       <c r="M42" s="26" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N42" s="26" t="n">
-        <v>285</v>
+        <v>155</v>
       </c>
       <c r="O42" s="27" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="P42" s="27" t="n">
-        <v>4605</v>
+        <v>2794</v>
       </c>
       <c r="Q42" s="28" t="inlineStr">
         <is>
@@ -3095,37 +3085,37 @@
         </is>
       </c>
       <c r="F43" s="22" t="n">
-        <v>23638</v>
+        <v>6763</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>70.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>16743</v>
+        <v>4863</v>
       </c>
       <c r="I43" s="24" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="J43" s="24" t="n">
-        <v>6286</v>
+        <v>1729</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>506</v>
+        <v>117</v>
       </c>
       <c r="M43" s="26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="N43" s="26" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="O43" s="27" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="P43" s="27" t="n">
-        <v>6895</v>
+        <v>1900</v>
       </c>
       <c r="Q43" s="28" t="inlineStr">
         <is>
@@ -3144,37 +3134,37 @@
         </is>
       </c>
       <c r="F44" s="22" t="n">
-        <v>3695</v>
+        <v>985</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>61.4</v>
+        <v>59.3</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>2270</v>
+        <v>584</v>
       </c>
       <c r="I44" s="24" t="n">
-        <v>36.1</v>
+        <v>38.2</v>
       </c>
       <c r="J44" s="24" t="n">
-        <v>1333</v>
+        <v>376</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="M44" s="26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N44" s="26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O44" s="27" t="n">
-        <v>38.5</v>
+        <v>40.6</v>
       </c>
       <c r="P44" s="27" t="n">
-        <v>1422</v>
+        <v>400</v>
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
@@ -3193,37 +3183,37 @@
         </is>
       </c>
       <c r="F45" s="22" t="n">
-        <v>37521</v>
+        <v>13517</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>69.7</v>
+        <v>64.7</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>26154</v>
+        <v>8752</v>
       </c>
       <c r="I45" s="24" t="n">
-        <v>26.4</v>
+        <v>31.6</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>9907</v>
+        <v>4266</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>1117</v>
+        <v>349</v>
       </c>
       <c r="M45" s="26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N45" s="26" t="n">
-        <v>371</v>
+        <v>155</v>
       </c>
       <c r="O45" s="27" t="n">
-        <v>30.4</v>
+        <v>35.3</v>
       </c>
       <c r="P45" s="27" t="n">
-        <v>11396</v>
+        <v>4771</v>
       </c>
       <c r="Q45" s="28" t="inlineStr">
         <is>
@@ -3242,37 +3232,37 @@
         </is>
       </c>
       <c r="F46" s="22" t="n">
-        <v>2539</v>
+        <v>1387</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>40.8</v>
+        <v>43.4</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>1036</v>
+        <v>603</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>52.8</v>
+        <v>50.9</v>
       </c>
       <c r="J46" s="24" t="n">
-        <v>1339</v>
+        <v>706</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="M46" s="26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="N46" s="26" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="O46" s="27" t="n">
-        <v>59.1</v>
+        <v>56.5</v>
       </c>
       <c r="P46" s="27" t="n">
-        <v>1501</v>
+        <v>784</v>
       </c>
       <c r="Q46" s="28" t="inlineStr">
         <is>
@@ -3291,37 +3281,37 @@
         </is>
       </c>
       <c r="F47" s="22" t="n">
-        <v>2031</v>
+        <v>82</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>51.7</v>
+        <v>40.2</v>
       </c>
       <c r="H47" s="23" t="n">
-        <v>1050</v>
+        <v>33</v>
       </c>
       <c r="I47" s="24" t="n">
-        <v>35.5</v>
+        <v>48.9</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>720</v>
+        <v>40</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="M47" s="26" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="N47" s="26" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="O47" s="27" t="n">
-        <v>48.3</v>
+        <v>59.9</v>
       </c>
       <c r="P47" s="27" t="n">
-        <v>981</v>
+        <v>49</v>
       </c>
       <c r="Q47" s="28" t="inlineStr">
         <is>
@@ -3340,25 +3330,25 @@
         </is>
       </c>
       <c r="F48" s="22" t="n">
-        <v>1820</v>
+        <v>1294</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>67.7</v>
+        <v>68.8</v>
       </c>
       <c r="H48" s="23" t="n">
-        <v>1232</v>
+        <v>891</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="J48" s="24" t="n">
-        <v>546</v>
+        <v>367</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M48" s="26" t="n">
         <v>0</v>
@@ -3367,10 +3357,10 @@
         <v>0</v>
       </c>
       <c r="O48" s="27" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="P48" s="27" t="n">
-        <v>588</v>
+        <v>404</v>
       </c>
       <c r="Q48" s="28" t="inlineStr">
         <is>
@@ -3389,25 +3379,25 @@
         </is>
       </c>
       <c r="F49" s="22" t="n">
-        <v>16567</v>
+        <v>4404</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="H49" s="23" t="n">
-        <v>6495</v>
+        <v>1739</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>55.3</v>
+        <v>55.8</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>9162</v>
+        <v>2460</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>911</v>
+        <v>206</v>
       </c>
       <c r="M49" s="26" t="n">
         <v>0</v>
@@ -3416,10 +3406,10 @@
         <v>0</v>
       </c>
       <c r="O49" s="27" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
       <c r="P49" s="27" t="n">
-        <v>10073</v>
+        <v>2665</v>
       </c>
       <c r="Q49" s="28" t="inlineStr">
         <is>
@@ -3438,41 +3428,31 @@
         </is>
       </c>
       <c r="F50" s="22" t="n">
-        <v>87</v>
-      </c>
-      <c r="G50" s="23" t="n">
-        <v>72.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="23" t="n">
-        <v>63</v>
-      </c>
-      <c r="I50" s="24" t="n">
-        <v>23.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I50" s="24" t="inlineStr"/>
       <c r="J50" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="K50" s="25" t="n">
-        <v>4.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K50" s="25" t="inlineStr"/>
       <c r="L50" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M50" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M50" s="26" t="inlineStr"/>
       <c r="N50" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O50" s="27" t="n">
-        <v>27.8</v>
-      </c>
+      <c r="O50" s="27" t="inlineStr"/>
       <c r="P50" s="27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3487,37 +3467,37 @@
         </is>
       </c>
       <c r="F51" s="22" t="n">
-        <v>28185</v>
+        <v>4359</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>69.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="H51" s="23" t="n">
-        <v>19630</v>
+        <v>3119</v>
       </c>
       <c r="I51" s="24" t="n">
-        <v>29.2</v>
+        <v>27.1</v>
       </c>
       <c r="J51" s="24" t="n">
-        <v>8233</v>
+        <v>1181</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="M51" s="26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N51" s="26" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="O51" s="27" t="n">
-        <v>30.4</v>
+        <v>28.5</v>
       </c>
       <c r="P51" s="27" t="n">
-        <v>8556</v>
+        <v>1241</v>
       </c>
       <c r="Q51" s="28" t="inlineStr">
         <is>
@@ -3536,37 +3516,37 @@
         </is>
       </c>
       <c r="F52" s="22" t="n">
-        <v>43055</v>
+        <v>11294</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="H52" s="23" t="n">
-        <v>23320</v>
+        <v>6105</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>37.9</v>
+        <v>39.5</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>16337</v>
+        <v>4458</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>1485</v>
+        <v>374</v>
       </c>
       <c r="M52" s="26" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N52" s="26" t="n">
-        <v>1909</v>
+        <v>353</v>
       </c>
       <c r="O52" s="27" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="P52" s="27" t="n">
-        <v>19732</v>
+        <v>5185</v>
       </c>
       <c r="Q52" s="28" t="inlineStr">
         <is>
@@ -3585,37 +3565,37 @@
         </is>
       </c>
       <c r="F53" s="22" t="n">
-        <v>15765</v>
+        <v>271</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>23.6</v>
+        <v>20.8</v>
       </c>
       <c r="H53" s="23" t="n">
-        <v>3728</v>
+        <v>56</v>
       </c>
       <c r="I53" s="24" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>10909</v>
+        <v>203</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>814</v>
+        <v>8</v>
       </c>
       <c r="M53" s="26" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="N53" s="26" t="n">
-        <v>329</v>
+        <v>3</v>
       </c>
       <c r="O53" s="27" t="n">
-        <v>76.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="P53" s="27" t="n">
-        <v>12052</v>
+        <v>215</v>
       </c>
       <c r="Q53" s="28" t="inlineStr">
         <is>
@@ -3634,37 +3614,37 @@
         </is>
       </c>
       <c r="F54" s="22" t="n">
-        <v>17529</v>
+        <v>7020</v>
       </c>
       <c r="G54" s="23" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
       <c r="H54" s="23" t="n">
-        <v>8419</v>
+        <v>3458</v>
       </c>
       <c r="I54" s="24" t="n">
-        <v>47.7</v>
+        <v>45.9</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>8361</v>
+        <v>3222</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>714</v>
+        <v>305</v>
       </c>
       <c r="M54" s="26" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N54" s="26" t="n">
         <v>31</v>
       </c>
       <c r="O54" s="27" t="n">
-        <v>51.9</v>
+        <v>50.7</v>
       </c>
       <c r="P54" s="27" t="n">
-        <v>9106</v>
+        <v>3557</v>
       </c>
       <c r="Q54" s="28" t="inlineStr">
         <is>
@@ -3683,37 +3663,37 @@
         </is>
       </c>
       <c r="F55" s="22" t="n">
-        <v>12963</v>
+        <v>713</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>48.6</v>
+        <v>27.1</v>
       </c>
       <c r="H55" s="23" t="n">
-        <v>6294</v>
+        <v>194</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>47.5</v>
+        <v>59.6</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>6158</v>
+        <v>425</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>309</v>
+        <v>88</v>
       </c>
       <c r="M55" s="26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N55" s="26" t="n">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="O55" s="27" t="n">
-        <v>51.3</v>
+        <v>72.8</v>
       </c>
       <c r="P55" s="27" t="n">
-        <v>6656</v>
+        <v>519</v>
       </c>
       <c r="Q55" s="28" t="inlineStr">
         <is>
@@ -3732,37 +3712,37 @@
         </is>
       </c>
       <c r="F56" s="22" t="n">
-        <v>38177</v>
+        <v>1532</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>68.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H56" s="23" t="n">
-        <v>26020</v>
+        <v>1028</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>28.7</v>
+        <v>29.9</v>
       </c>
       <c r="J56" s="24" t="n">
-        <v>10938</v>
+        <v>458</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>907</v>
+        <v>28</v>
       </c>
       <c r="M56" s="26" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="N56" s="26" t="n">
-        <v>311</v>
+        <v>18</v>
       </c>
       <c r="O56" s="27" t="n">
-        <v>31.8</v>
+        <v>32.9</v>
       </c>
       <c r="P56" s="27" t="n">
-        <v>12157</v>
+        <v>504</v>
       </c>
       <c r="Q56" s="28" t="inlineStr">
         <is>
@@ -3781,37 +3761,37 @@
         </is>
       </c>
       <c r="F57" s="22" t="n">
-        <v>21686</v>
+        <v>235</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>22.9</v>
+        <v>23.7</v>
       </c>
       <c r="H57" s="23" t="n">
-        <v>4968</v>
+        <v>56</v>
       </c>
       <c r="I57" s="24" t="n">
-        <v>55</v>
+        <v>54.4</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>11926</v>
+        <v>128</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>2777</v>
+        <v>31</v>
       </c>
       <c r="M57" s="26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="N57" s="26" t="n">
-        <v>1993</v>
+        <v>20</v>
       </c>
       <c r="O57" s="27" t="n">
-        <v>77</v>
+        <v>76.2</v>
       </c>
       <c r="P57" s="27" t="n">
-        <v>16696</v>
+        <v>179</v>
       </c>
       <c r="Q57" s="28" t="inlineStr">
         <is>
@@ -3830,37 +3810,37 @@
         </is>
       </c>
       <c r="F58" s="22" t="n">
-        <v>11199</v>
+        <v>945</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>30.2</v>
+        <v>32.8</v>
       </c>
       <c r="H58" s="23" t="n">
-        <v>3387</v>
+        <v>310</v>
       </c>
       <c r="I58" s="24" t="n">
-        <v>61.1</v>
+        <v>58.9</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>6843</v>
+        <v>557</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>508</v>
+        <v>36</v>
       </c>
       <c r="M58" s="26" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N58" s="26" t="n">
-        <v>462</v>
+        <v>42</v>
       </c>
       <c r="O58" s="27" t="n">
-        <v>69.8</v>
+        <v>67.2</v>
       </c>
       <c r="P58" s="27" t="n">
-        <v>7813</v>
+        <v>635</v>
       </c>
       <c r="Q58" s="28" t="inlineStr">
         <is>
@@ -3879,37 +3859,37 @@
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>6344</v>
+        <v>3722</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>67.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="H59" s="23" t="n">
-        <v>4289</v>
+        <v>2446</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>27.2</v>
+        <v>28.3</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>1723</v>
+        <v>1055</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="M59" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="N59" s="26" t="n">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="O59" s="27" t="n">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="P59" s="27" t="n">
-        <v>2049</v>
+        <v>1273</v>
       </c>
       <c r="Q59" s="28" t="inlineStr">
         <is>
@@ -3928,37 +3908,37 @@
         </is>
       </c>
       <c r="F60" s="22" t="n">
-        <v>9981</v>
+        <v>7021</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="H60" s="23" t="n">
-        <v>5671</v>
+        <v>4070</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>37.6</v>
+        <v>36.7</v>
       </c>
       <c r="J60" s="24" t="n">
-        <v>3753</v>
+        <v>2575</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>378</v>
+        <v>257</v>
       </c>
       <c r="M60" s="26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="N60" s="26" t="n">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="O60" s="27" t="n">
-        <v>43.2</v>
+        <v>42</v>
       </c>
       <c r="P60" s="27" t="n">
-        <v>4309</v>
+        <v>2951</v>
       </c>
       <c r="Q60" s="28" t="inlineStr">
         <is>
@@ -4075,37 +4055,37 @@
         </is>
       </c>
       <c r="F63" s="22" t="n">
-        <v>10178</v>
+        <v>4098</v>
       </c>
       <c r="G63" s="23" t="n">
-        <v>28.6</v>
+        <v>24.3</v>
       </c>
       <c r="H63" s="23" t="n">
-        <v>2911</v>
+        <v>996</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>38.6</v>
+        <v>45.9</v>
       </c>
       <c r="J63" s="24" t="n">
-        <v>3932</v>
+        <v>1883</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>314</v>
+        <v>108</v>
       </c>
       <c r="M63" s="26" t="n">
-        <v>29.8</v>
+        <v>27.2</v>
       </c>
       <c r="N63" s="26" t="n">
-        <v>3029</v>
+        <v>1114</v>
       </c>
       <c r="O63" s="27" t="n">
-        <v>71.5</v>
+        <v>75.8</v>
       </c>
       <c r="P63" s="27" t="n">
-        <v>7276</v>
+        <v>3104</v>
       </c>
       <c r="Q63" s="28" t="inlineStr">
         <is>
@@ -4124,37 +4104,37 @@
         </is>
       </c>
       <c r="F64" s="22" t="n">
-        <v>1051</v>
+        <v>735</v>
       </c>
       <c r="G64" s="23" t="n">
-        <v>66.8</v>
+        <v>68</v>
       </c>
       <c r="H64" s="23" t="n">
-        <v>702</v>
+        <v>500</v>
       </c>
       <c r="I64" s="24" t="n">
-        <v>25.4</v>
+        <v>24.3</v>
       </c>
       <c r="J64" s="24" t="n">
-        <v>267</v>
+        <v>179</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="L64" s="25" t="n">
         <v>30</v>
       </c>
       <c r="M64" s="26" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="N64" s="26" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="O64" s="27" t="n">
-        <v>33.2</v>
+        <v>32</v>
       </c>
       <c r="P64" s="27" t="n">
-        <v>350</v>
+        <v>235</v>
       </c>
       <c r="Q64" s="28" t="inlineStr">
         <is>
@@ -4173,37 +4153,37 @@
         </is>
       </c>
       <c r="F65" s="22" t="n">
-        <v>1092</v>
+        <v>553</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>35.4</v>
+        <v>42.9</v>
       </c>
       <c r="H65" s="23" t="n">
-        <v>386</v>
+        <v>237</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="J65" s="24" t="n">
-        <v>510</v>
+        <v>237</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="L65" s="25" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="M65" s="26" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="N65" s="26" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="O65" s="27" t="n">
-        <v>64.7</v>
+        <v>57.2</v>
       </c>
       <c r="P65" s="27" t="n">
-        <v>706</v>
+        <v>316</v>
       </c>
       <c r="Q65" s="28" t="inlineStr">
         <is>
@@ -4222,37 +4202,37 @@
         </is>
       </c>
       <c r="F66" s="22" t="n">
-        <v>78586</v>
+        <v>23721</v>
       </c>
       <c r="G66" s="23" t="n">
-        <v>69.5</v>
+        <v>68.3</v>
       </c>
       <c r="H66" s="23" t="n">
-        <v>54586</v>
+        <v>16213</v>
       </c>
       <c r="I66" s="24" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
       </c>
       <c r="J66" s="24" t="n">
-        <v>20740</v>
+        <v>6133</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>3072</v>
+        <v>1187</v>
       </c>
       <c r="M66" s="26" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="N66" s="26" t="n">
         <v>188</v>
       </c>
       <c r="O66" s="27" t="n">
-        <v>30.5</v>
+        <v>31.7</v>
       </c>
       <c r="P66" s="27" t="n">
-        <v>24000</v>
+        <v>7508</v>
       </c>
       <c r="Q66" s="28" t="inlineStr">
         <is>
@@ -4271,25 +4251,25 @@
         </is>
       </c>
       <c r="F67" s="22" t="n">
-        <v>187572</v>
+        <v>8044</v>
       </c>
       <c r="G67" s="23" t="n">
-        <v>67.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="H67" s="23" t="n">
-        <v>127420</v>
+        <v>6129</v>
       </c>
       <c r="I67" s="24" t="n">
-        <v>24.7</v>
+        <v>18.6</v>
       </c>
       <c r="J67" s="24" t="n">
-        <v>46353</v>
+        <v>1496</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="L67" s="25" t="n">
-        <v>13799</v>
+        <v>419</v>
       </c>
       <c r="M67" s="26" t="n">
         <v>0</v>
@@ -4298,10 +4278,10 @@
         <v>0</v>
       </c>
       <c r="O67" s="27" t="n">
-        <v>32.1</v>
+        <v>23.8</v>
       </c>
       <c r="P67" s="27" t="n">
-        <v>60152</v>
+        <v>1916</v>
       </c>
       <c r="Q67" s="28" t="inlineStr">
         <is>
@@ -4320,37 +4300,37 @@
         </is>
       </c>
       <c r="F68" s="22" t="n">
-        <v>180620</v>
+        <v>35114</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>63.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H68" s="23" t="n">
-        <v>114115</v>
+        <v>24629</v>
       </c>
       <c r="I68" s="24" t="n">
-        <v>34.8</v>
+        <v>28.7</v>
       </c>
       <c r="J68" s="24" t="n">
-        <v>62889</v>
+        <v>10070</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L68" s="25" t="n">
-        <v>663</v>
+        <v>81</v>
       </c>
       <c r="M68" s="26" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="N68" s="26" t="n">
-        <v>2953</v>
+        <v>334</v>
       </c>
       <c r="O68" s="27" t="n">
-        <v>36.8</v>
+        <v>29.9</v>
       </c>
       <c r="P68" s="27" t="n">
-        <v>66504</v>
+        <v>10485</v>
       </c>
       <c r="Q68" s="28" t="inlineStr">
         <is>
@@ -4369,25 +4349,25 @@
         </is>
       </c>
       <c r="F69" s="29" t="n">
-        <v>39704</v>
+        <v>536</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>85.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H69" s="30" t="n">
-        <v>34078</v>
+        <v>445</v>
       </c>
       <c r="I69" s="31" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="J69" s="31" t="n">
-        <v>5487</v>
+        <v>69</v>
       </c>
       <c r="K69" s="32" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="L69" s="32" t="n">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="M69" s="33" t="n">
         <v>0</v>
@@ -4396,10 +4376,10 @@
         <v>0</v>
       </c>
       <c r="O69" s="34" t="n">
-        <v>14.2</v>
+        <v>17.1</v>
       </c>
       <c r="P69" s="34" t="n">
-        <v>5627</v>
+        <v>92</v>
       </c>
       <c r="Q69" s="28" t="inlineStr">
         <is>
@@ -4542,25 +4522,25 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>19514</v>
+        <v>2088</v>
       </c>
       <c r="H6" s="23" t="n">
         <v>60.9</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>11881</v>
+        <v>1271</v>
       </c>
       <c r="J6" s="24" t="n">
         <v>28.2</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>5512</v>
+        <v>590</v>
       </c>
       <c r="L6" s="25" t="n">
         <v>10.9</v>
       </c>
       <c r="M6" s="25" t="n">
-        <v>2122</v>
+        <v>227</v>
       </c>
       <c r="N6" s="26" t="n">
         <v>0</v>
@@ -4572,7 +4552,7 @@
         <v>39.1</v>
       </c>
       <c r="Q6" s="27" t="n">
-        <v>7634</v>
+        <v>817</v>
       </c>
       <c r="R6" s="28" t="inlineStr">
         <is>
@@ -4596,19 +4576,19 @@
         </is>
       </c>
       <c r="G7" s="22" t="n">
-        <v>632</v>
+        <v>315</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>63.8</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>403</v>
+        <v>201</v>
       </c>
       <c r="J7" s="24" t="n">
         <v>28</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="L7" s="25" t="n">
         <v>0</v>
@@ -4620,13 +4600,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P7" s="27" t="n">
         <v>36.2</v>
       </c>
       <c r="Q7" s="27" t="n">
-        <v>229</v>
+        <v>114</v>
       </c>
       <c r="R7" s="28" t="inlineStr">
         <is>
@@ -4650,25 +4630,25 @@
         </is>
       </c>
       <c r="G8" s="22" t="n">
-        <v>66817</v>
+        <v>11951</v>
       </c>
       <c r="H8" s="23" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>46732</v>
+        <v>8359</v>
       </c>
       <c r="J8" s="24" t="n">
         <v>26.6</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>17788</v>
+        <v>3182</v>
       </c>
       <c r="L8" s="25" t="n">
         <v>3.4</v>
       </c>
       <c r="M8" s="25" t="n">
-        <v>2296</v>
+        <v>411</v>
       </c>
       <c r="N8" s="26" t="n">
         <v>0</v>
@@ -4680,7 +4660,7 @@
         <v>30.1</v>
       </c>
       <c r="Q8" s="27" t="n">
-        <v>20084</v>
+        <v>3592</v>
       </c>
       <c r="R8" s="28" t="inlineStr">
         <is>
@@ -4704,25 +4684,25 @@
         </is>
       </c>
       <c r="G9" s="22" t="n">
-        <v>185155</v>
+        <v>5627</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>125094</v>
+        <v>3802</v>
       </c>
       <c r="J9" s="24" t="n">
         <v>25</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>46263</v>
+        <v>1406</v>
       </c>
       <c r="L9" s="25" t="n">
         <v>7.5</v>
       </c>
       <c r="M9" s="25" t="n">
-        <v>13799</v>
+        <v>419</v>
       </c>
       <c r="N9" s="26" t="n">
         <v>0</v>
@@ -4734,7 +4714,7 @@
         <v>32.4</v>
       </c>
       <c r="Q9" s="27" t="n">
-        <v>60061</v>
+        <v>1825</v>
       </c>
       <c r="R9" s="28" t="inlineStr">
         <is>
@@ -4758,25 +4738,25 @@
         </is>
       </c>
       <c r="G10" s="22" t="n">
-        <v>39565</v>
+        <v>397</v>
       </c>
       <c r="H10" s="23" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>33974</v>
+        <v>341</v>
       </c>
       <c r="J10" s="24" t="n">
         <v>13.8</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>5473</v>
+        <v>55</v>
       </c>
       <c r="L10" s="25" t="n">
         <v>0.3</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="N10" s="26" t="n">
         <v>0</v>
@@ -4788,7 +4768,7 @@
         <v>14.1</v>
       </c>
       <c r="Q10" s="27" t="n">
-        <v>5591</v>
+        <v>56</v>
       </c>
       <c r="R10" s="28" t="inlineStr">
         <is>
@@ -4812,25 +4792,25 @@
         </is>
       </c>
       <c r="G11" s="22" t="n">
-        <v>47512</v>
+        <v>1447</v>
       </c>
       <c r="H11" s="23" t="n">
         <v>56.1</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>26654</v>
+        <v>812</v>
       </c>
       <c r="J11" s="24" t="n">
         <v>42.9</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>20383</v>
+        <v>621</v>
       </c>
       <c r="L11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>475</v>
+        <v>14</v>
       </c>
       <c r="N11" s="26" t="n">
         <v>0</v>
@@ -4842,7 +4822,7 @@
         <v>43.9</v>
       </c>
       <c r="Q11" s="27" t="n">
-        <v>20858</v>
+        <v>635</v>
       </c>
       <c r="R11" s="28" t="inlineStr">
         <is>
@@ -4866,37 +4846,37 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>11453</v>
+        <v>115</v>
       </c>
       <c r="H12" s="23" t="n">
         <v>59.1</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>6769</v>
+        <v>68</v>
       </c>
       <c r="J12" s="24" t="n">
         <v>39</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>4467</v>
+        <v>45</v>
       </c>
       <c r="L12" s="25" t="n">
         <v>1.6</v>
       </c>
       <c r="M12" s="25" t="n">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="N12" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>40.9</v>
       </c>
       <c r="Q12" s="27" t="n">
-        <v>4684</v>
+        <v>47</v>
       </c>
       <c r="R12" s="28" t="inlineStr">
         <is>
@@ -4920,37 +4900,37 @@
         </is>
       </c>
       <c r="G13" s="22" t="n">
-        <v>23386</v>
+        <v>719</v>
       </c>
       <c r="H13" s="23" t="n">
         <v>43.8</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>10243</v>
+        <v>315</v>
       </c>
       <c r="J13" s="24" t="n">
         <v>52.1</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>12184</v>
+        <v>375</v>
       </c>
       <c r="L13" s="25" t="n">
         <v>3.8</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>889</v>
+        <v>27</v>
       </c>
       <c r="N13" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="P13" s="27" t="n">
         <v>56.2</v>
       </c>
       <c r="Q13" s="27" t="n">
-        <v>13143</v>
+        <v>404</v>
       </c>
       <c r="R13" s="28" t="inlineStr">
         <is>
@@ -4974,25 +4954,25 @@
         </is>
       </c>
       <c r="G14" s="22" t="n">
-        <v>6728</v>
+        <v>0</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>27.8</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="J14" s="24" t="n">
         <v>66</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>4440</v>
+        <v>0</v>
       </c>
       <c r="L14" s="25" t="n">
         <v>6.1</v>
       </c>
       <c r="M14" s="25" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="N14" s="26" t="n">
         <v>0</v>
@@ -5004,7 +4984,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="Q14" s="27" t="n">
-        <v>4851</v>
+        <v>0</v>
       </c>
       <c r="R14" s="28" t="inlineStr">
         <is>
@@ -5028,25 +5008,25 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>59007</v>
+        <v>6467</v>
       </c>
       <c r="H15" s="23" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>45967</v>
+        <v>5038</v>
       </c>
       <c r="J15" s="24" t="n">
         <v>20.7</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>12214</v>
+        <v>1339</v>
       </c>
       <c r="L15" s="25" t="n">
         <v>1.3</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>767</v>
+        <v>84</v>
       </c>
       <c r="N15" s="26" t="n">
         <v>0</v>
@@ -5058,7 +5038,7 @@
         <v>22</v>
       </c>
       <c r="Q15" s="27" t="n">
-        <v>12982</v>
+        <v>1423</v>
       </c>
       <c r="R15" s="28" t="inlineStr">
         <is>
@@ -5082,25 +5062,25 @@
         </is>
       </c>
       <c r="G16" s="22" t="n">
-        <v>11670</v>
+        <v>360</v>
       </c>
       <c r="H16" s="23" t="n">
         <v>50.5</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>5893</v>
+        <v>182</v>
       </c>
       <c r="J16" s="24" t="n">
         <v>48.6</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>5672</v>
+        <v>175</v>
       </c>
       <c r="L16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="N16" s="26" t="n">
         <v>0</v>
@@ -5112,7 +5092,7 @@
         <v>49.6</v>
       </c>
       <c r="Q16" s="27" t="n">
-        <v>5788</v>
+        <v>178</v>
       </c>
       <c r="R16" s="28" t="inlineStr">
         <is>
@@ -5136,37 +5116,37 @@
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>15651</v>
+        <v>158</v>
       </c>
       <c r="H17" s="23" t="n">
         <v>23.7</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>3709</v>
+        <v>37</v>
       </c>
       <c r="J17" s="24" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>10815</v>
+        <v>109</v>
       </c>
       <c r="L17" s="25" t="n">
         <v>5.2</v>
       </c>
       <c r="M17" s="25" t="n">
-        <v>814</v>
+        <v>8</v>
       </c>
       <c r="N17" s="26" t="n">
         <v>2.1</v>
       </c>
       <c r="O17" s="26" t="n">
-        <v>329</v>
+        <v>3</v>
       </c>
       <c r="P17" s="27" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="Q17" s="27" t="n">
-        <v>11958</v>
+        <v>120</v>
       </c>
       <c r="R17" s="28" t="inlineStr">
         <is>
@@ -5190,37 +5170,37 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>21667</v>
+        <v>217</v>
       </c>
       <c r="H18" s="23" t="n">
         <v>22.9</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>4962</v>
+        <v>50</v>
       </c>
       <c r="J18" s="24" t="n">
         <v>55</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>11917</v>
+        <v>119</v>
       </c>
       <c r="L18" s="25" t="n">
         <v>12.8</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>2773</v>
+        <v>28</v>
       </c>
       <c r="N18" s="26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="O18" s="26" t="n">
-        <v>1993</v>
+        <v>20</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>77</v>
       </c>
       <c r="Q18" s="27" t="n">
-        <v>16684</v>
+        <v>167</v>
       </c>
       <c r="R18" s="28" t="inlineStr">
         <is>
@@ -5244,37 +5224,37 @@
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>2852</v>
+        <v>594</v>
       </c>
       <c r="H19" s="23" t="n">
         <v>31.1</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>887</v>
+        <v>185</v>
       </c>
       <c r="J19" s="24" t="n">
         <v>60.9</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>1737</v>
+        <v>362</v>
       </c>
       <c r="L19" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N19" s="26" t="n">
         <v>7.6</v>
       </c>
       <c r="O19" s="26" t="n">
-        <v>217</v>
+        <v>45</v>
       </c>
       <c r="P19" s="27" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="Q19" s="27" t="n">
-        <v>1965</v>
+        <v>410</v>
       </c>
       <c r="R19" s="28" t="inlineStr">
         <is>
@@ -5298,37 +5278,37 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>19945</v>
+        <v>2134</v>
       </c>
       <c r="H20" s="23" t="n">
         <v>62.8</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>12525</v>
+        <v>1340</v>
       </c>
       <c r="J20" s="24" t="n">
         <v>30.7</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>6123</v>
+        <v>655</v>
       </c>
       <c r="L20" s="25" t="n">
         <v>3.7</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>738</v>
+        <v>79</v>
       </c>
       <c r="N20" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="O20" s="26" t="n">
-        <v>558</v>
+        <v>60</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>37.2</v>
       </c>
       <c r="Q20" s="27" t="n">
-        <v>7420</v>
+        <v>794</v>
       </c>
       <c r="R20" s="28" t="inlineStr">
         <is>
@@ -5352,37 +5332,37 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>26666</v>
+        <v>2960</v>
       </c>
       <c r="H21" s="23" t="n">
         <v>65.8</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>17546</v>
+        <v>1947</v>
       </c>
       <c r="J21" s="24" t="n">
         <v>31.5</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>8400</v>
+        <v>932</v>
       </c>
       <c r="L21" s="25" t="n">
         <v>1.8</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>480</v>
+        <v>53</v>
       </c>
       <c r="N21" s="26" t="n">
         <v>0.9</v>
       </c>
       <c r="O21" s="26" t="n">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="P21" s="27" t="n">
         <v>34.2</v>
       </c>
       <c r="Q21" s="27" t="n">
-        <v>9120</v>
+        <v>1012</v>
       </c>
       <c r="R21" s="28" t="inlineStr">
         <is>
@@ -5406,37 +5386,37 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>13284</v>
+        <v>403</v>
       </c>
       <c r="H22" s="23" t="n">
         <v>23.2</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>3082</v>
+        <v>94</v>
       </c>
       <c r="J22" s="24" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>9817</v>
+        <v>298</v>
       </c>
       <c r="L22" s="25" t="n">
         <v>1.9</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>252</v>
+        <v>8</v>
       </c>
       <c r="N22" s="26" t="n">
         <v>1</v>
       </c>
       <c r="O22" s="26" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>76.8</v>
       </c>
       <c r="Q22" s="27" t="n">
-        <v>10202</v>
+        <v>310</v>
       </c>
       <c r="R22" s="28" t="inlineStr">
         <is>
@@ -5460,37 +5440,37 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>23014</v>
+        <v>3857</v>
       </c>
       <c r="H23" s="23" t="n">
         <v>58</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>13348</v>
+        <v>2237</v>
       </c>
       <c r="J23" s="24" t="n">
         <v>31.1</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>7157</v>
+        <v>1200</v>
       </c>
       <c r="L23" s="25" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>2002</v>
+        <v>336</v>
       </c>
       <c r="N23" s="26" t="n">
         <v>2.3</v>
       </c>
       <c r="O23" s="26" t="n">
-        <v>529</v>
+        <v>89</v>
       </c>
       <c r="P23" s="27" t="n">
         <v>42.1</v>
       </c>
       <c r="Q23" s="27" t="n">
-        <v>9689</v>
+        <v>1624</v>
       </c>
       <c r="R23" s="28" t="inlineStr">
         <is>
@@ -5514,37 +5494,37 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>33869</v>
+        <v>3595</v>
       </c>
       <c r="H24" s="23" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>23336</v>
+        <v>2477</v>
       </c>
       <c r="J24" s="24" t="n">
         <v>28</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>9483</v>
+        <v>1006</v>
       </c>
       <c r="L24" s="25" t="n">
         <v>1.7</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>576</v>
+        <v>61</v>
       </c>
       <c r="N24" s="26" t="n">
         <v>1.4</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>474</v>
+        <v>50</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>31.1</v>
       </c>
       <c r="Q24" s="27" t="n">
-        <v>10533</v>
+        <v>1118</v>
       </c>
       <c r="R24" s="28" t="inlineStr">
         <is>
@@ -5568,37 +5548,37 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>14368</v>
+        <v>440</v>
       </c>
       <c r="H25" s="23" t="n">
         <v>44.6</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>6408</v>
+        <v>196</v>
       </c>
       <c r="J25" s="24" t="n">
         <v>40.7</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>5848</v>
+        <v>179</v>
       </c>
       <c r="L25" s="25" t="n">
         <v>9.9</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>1422</v>
+        <v>44</v>
       </c>
       <c r="N25" s="26" t="n">
         <v>4.8</v>
       </c>
       <c r="O25" s="26" t="n">
-        <v>690</v>
+        <v>21</v>
       </c>
       <c r="P25" s="27" t="n">
         <v>55.4</v>
       </c>
       <c r="Q25" s="27" t="n">
-        <v>7960</v>
+        <v>244</v>
       </c>
       <c r="R25" s="28" t="inlineStr">
         <is>
@@ -5622,37 +5602,37 @@
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>7594</v>
+        <v>1272</v>
       </c>
       <c r="H26" s="23" t="n">
         <v>49.7</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>3774</v>
+        <v>632</v>
       </c>
       <c r="J26" s="24" t="n">
         <v>42.8</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>3250</v>
+        <v>545</v>
       </c>
       <c r="L26" s="25" t="n">
         <v>1.7</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="N26" s="26" t="n">
         <v>5.8</v>
       </c>
       <c r="O26" s="26" t="n">
-        <v>440</v>
+        <v>74</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>50.3</v>
       </c>
       <c r="Q26" s="27" t="n">
-        <v>3820</v>
+        <v>640</v>
       </c>
       <c r="R26" s="28" t="inlineStr">
         <is>
@@ -5676,37 +5656,37 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>56030</v>
+        <v>6193</v>
       </c>
       <c r="H27" s="23" t="n">
         <v>36.8</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>20619</v>
+        <v>2279</v>
       </c>
       <c r="J27" s="24" t="n">
         <v>61.5</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>34458</v>
+        <v>3809</v>
       </c>
       <c r="L27" s="25" t="n">
         <v>1.3</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>728</v>
+        <v>81</v>
       </c>
       <c r="N27" s="26" t="n">
         <v>0.4</v>
       </c>
       <c r="O27" s="26" t="n">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="P27" s="27" t="n">
         <v>63.2</v>
       </c>
       <c r="Q27" s="27" t="n">
-        <v>35411</v>
+        <v>3914</v>
       </c>
       <c r="R27" s="28" t="inlineStr">
         <is>
@@ -5730,37 +5710,37 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>18230</v>
+        <v>3044</v>
       </c>
       <c r="H28" s="23" t="n">
         <v>47.3</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>8623</v>
+        <v>1440</v>
       </c>
       <c r="J28" s="24" t="n">
         <v>45.3</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>8258</v>
+        <v>1379</v>
       </c>
       <c r="L28" s="25" t="n">
         <v>1.3</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="N28" s="26" t="n">
         <v>6.1</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>1112</v>
+        <v>186</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>52.7</v>
       </c>
       <c r="Q28" s="27" t="n">
-        <v>9607</v>
+        <v>1604</v>
       </c>
       <c r="R28" s="28" t="inlineStr">
         <is>
@@ -5784,37 +5764,37 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>11151</v>
+        <v>2062</v>
       </c>
       <c r="H29" s="23" t="n">
         <v>61.9</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>6903</v>
+        <v>1277</v>
       </c>
       <c r="J29" s="24" t="n">
         <v>36.2</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>4037</v>
+        <v>747</v>
       </c>
       <c r="L29" s="25" t="n">
         <v>0.7</v>
       </c>
       <c r="M29" s="25" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="N29" s="26" t="n">
         <v>1.1</v>
       </c>
       <c r="O29" s="26" t="n">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="P29" s="27" t="n">
         <v>38</v>
       </c>
       <c r="Q29" s="27" t="n">
-        <v>4238</v>
+        <v>784</v>
       </c>
       <c r="R29" s="28" t="inlineStr">
         <is>
@@ -5838,37 +5818,37 @@
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>10869</v>
+        <v>2076</v>
       </c>
       <c r="H30" s="23" t="n">
         <v>56.1</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>6098</v>
+        <v>1165</v>
       </c>
       <c r="J30" s="24" t="n">
         <v>34.5</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>3750</v>
+        <v>716</v>
       </c>
       <c r="L30" s="25" t="n">
         <v>4.7</v>
       </c>
       <c r="M30" s="25" t="n">
-        <v>511</v>
+        <v>98</v>
       </c>
       <c r="N30" s="26" t="n">
         <v>4.7</v>
       </c>
       <c r="O30" s="26" t="n">
-        <v>511</v>
+        <v>98</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>43.9</v>
       </c>
       <c r="Q30" s="27" t="n">
-        <v>4772</v>
+        <v>911</v>
       </c>
       <c r="R30" s="28" t="inlineStr">
         <is>
@@ -5892,37 +5872,37 @@
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>20302</v>
+        <v>9363</v>
       </c>
       <c r="H31" s="23" t="n">
         <v>70.40000000000001</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>14293</v>
+        <v>6591</v>
       </c>
       <c r="J31" s="24" t="n">
         <v>24.5</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>4974</v>
+        <v>2294</v>
       </c>
       <c r="L31" s="25" t="n">
         <v>3.7</v>
       </c>
       <c r="M31" s="25" t="n">
-        <v>751</v>
+        <v>346</v>
       </c>
       <c r="N31" s="26" t="n">
         <v>1.4</v>
       </c>
       <c r="O31" s="26" t="n">
-        <v>284</v>
+        <v>131</v>
       </c>
       <c r="P31" s="27" t="n">
         <v>29.6</v>
       </c>
       <c r="Q31" s="27" t="n">
-        <v>6009</v>
+        <v>2771</v>
       </c>
       <c r="R31" s="28" t="inlineStr">
         <is>
@@ -5946,37 +5926,37 @@
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>10847</v>
+        <v>4921</v>
       </c>
       <c r="H32" s="23" t="n">
         <v>51.7</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>5608</v>
+        <v>2544</v>
       </c>
       <c r="J32" s="24" t="n">
         <v>40.3</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>4371</v>
+        <v>1983</v>
       </c>
       <c r="L32" s="25" t="n">
         <v>6.8</v>
       </c>
       <c r="M32" s="25" t="n">
-        <v>738</v>
+        <v>335</v>
       </c>
       <c r="N32" s="26" t="n">
         <v>1.1</v>
       </c>
       <c r="O32" s="26" t="n">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>48.2</v>
       </c>
       <c r="Q32" s="27" t="n">
-        <v>5228</v>
+        <v>2372</v>
       </c>
       <c r="R32" s="28" t="inlineStr">
         <is>
@@ -6000,37 +5980,37 @@
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>23577</v>
+        <v>4272</v>
       </c>
       <c r="H33" s="23" t="n">
         <v>35.4</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>8346</v>
+        <v>1512</v>
       </c>
       <c r="J33" s="24" t="n">
         <v>53.3</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>12566</v>
+        <v>2277</v>
       </c>
       <c r="L33" s="25" t="n">
         <v>4.2</v>
       </c>
       <c r="M33" s="25" t="n">
-        <v>990</v>
+        <v>179</v>
       </c>
       <c r="N33" s="26" t="n">
         <v>7.1</v>
       </c>
       <c r="O33" s="26" t="n">
-        <v>1674</v>
+        <v>303</v>
       </c>
       <c r="P33" s="27" t="n">
         <v>64.59999999999999</v>
       </c>
       <c r="Q33" s="27" t="n">
-        <v>15230</v>
+        <v>2760</v>
       </c>
       <c r="R33" s="28" t="inlineStr">
         <is>
@@ -6054,37 +6034,37 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>1253</v>
+        <v>1080</v>
       </c>
       <c r="H34" s="23" t="n">
         <v>39.2</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="J34" s="24" t="n">
         <v>52.2</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>654</v>
+        <v>564</v>
       </c>
       <c r="L34" s="25" t="n">
         <v>7.2</v>
       </c>
       <c r="M34" s="25" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="N34" s="26" t="n">
         <v>1.4</v>
       </c>
       <c r="O34" s="26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>60.8</v>
       </c>
       <c r="Q34" s="27" t="n">
-        <v>762</v>
+        <v>656</v>
       </c>
       <c r="R34" s="28" t="inlineStr">
         <is>
@@ -6108,37 +6088,37 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>76486</v>
+        <v>4010</v>
       </c>
       <c r="H35" s="23" t="n">
         <v>47</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>35948</v>
+        <v>1885</v>
       </c>
       <c r="J35" s="24" t="n">
         <v>45.8</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>35031</v>
+        <v>1836</v>
       </c>
       <c r="L35" s="25" t="n">
         <v>4.5</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>3442</v>
+        <v>180</v>
       </c>
       <c r="N35" s="26" t="n">
         <v>2.6</v>
       </c>
       <c r="O35" s="26" t="n">
-        <v>1989</v>
+        <v>104</v>
       </c>
       <c r="P35" s="27" t="n">
         <v>52.9</v>
       </c>
       <c r="Q35" s="27" t="n">
-        <v>40461</v>
+        <v>2121</v>
       </c>
       <c r="R35" s="28" t="inlineStr">
         <is>
@@ -6162,37 +6142,37 @@
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>20864</v>
+        <v>210</v>
       </c>
       <c r="H36" s="23" t="n">
         <v>62</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>12936</v>
+        <v>130</v>
       </c>
       <c r="J36" s="24" t="n">
         <v>31.2</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>6510</v>
+        <v>65</v>
       </c>
       <c r="L36" s="25" t="n">
         <v>2.1</v>
       </c>
       <c r="M36" s="25" t="n">
-        <v>438</v>
+        <v>4</v>
       </c>
       <c r="N36" s="26" t="n">
         <v>4.8</v>
       </c>
       <c r="O36" s="26" t="n">
-        <v>1001</v>
+        <v>10</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>38.1</v>
       </c>
       <c r="Q36" s="27" t="n">
-        <v>7949</v>
+        <v>80</v>
       </c>
       <c r="R36" s="28" t="inlineStr">
         <is>
@@ -6216,37 +6196,37 @@
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>11030</v>
+        <v>334</v>
       </c>
       <c r="H37" s="23" t="n">
         <v>45.5</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>5019</v>
+        <v>152</v>
       </c>
       <c r="J37" s="24" t="n">
         <v>43</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>4743</v>
+        <v>144</v>
       </c>
       <c r="L37" s="25" t="n">
         <v>5.7</v>
       </c>
       <c r="M37" s="25" t="n">
-        <v>629</v>
+        <v>19</v>
       </c>
       <c r="N37" s="26" t="n">
         <v>5.7</v>
       </c>
       <c r="O37" s="26" t="n">
-        <v>629</v>
+        <v>19</v>
       </c>
       <c r="P37" s="27" t="n">
         <v>54.4</v>
       </c>
       <c r="Q37" s="27" t="n">
-        <v>6000</v>
+        <v>182</v>
       </c>
       <c r="R37" s="28" t="inlineStr">
         <is>
@@ -6270,37 +6250,37 @@
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>15503</v>
+        <v>156</v>
       </c>
       <c r="H38" s="23" t="n">
         <v>46.3</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>7178</v>
+        <v>72</v>
       </c>
       <c r="J38" s="24" t="n">
         <v>44.2</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>6852</v>
+        <v>69</v>
       </c>
       <c r="L38" s="25" t="n">
         <v>6.8</v>
       </c>
       <c r="M38" s="25" t="n">
-        <v>1054</v>
+        <v>11</v>
       </c>
       <c r="N38" s="26" t="n">
         <v>2.7</v>
       </c>
       <c r="O38" s="26" t="n">
-        <v>419</v>
+        <v>4</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>53.7</v>
       </c>
       <c r="Q38" s="27" t="n">
-        <v>8325</v>
+        <v>84</v>
       </c>
       <c r="R38" s="28" t="inlineStr">
         <is>
@@ -6324,37 +6304,37 @@
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>28067</v>
+        <v>855</v>
       </c>
       <c r="H39" s="23" t="n">
         <v>43</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>12069</v>
+        <v>368</v>
       </c>
       <c r="J39" s="24" t="n">
         <v>49.5</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>13893</v>
+        <v>423</v>
       </c>
       <c r="L39" s="25" t="n">
         <v>1.3</v>
       </c>
       <c r="M39" s="25" t="n">
-        <v>365</v>
+        <v>11</v>
       </c>
       <c r="N39" s="26" t="n">
         <v>6.2</v>
       </c>
       <c r="O39" s="26" t="n">
-        <v>1740</v>
+        <v>53</v>
       </c>
       <c r="P39" s="27" t="n">
         <v>57</v>
       </c>
       <c r="Q39" s="27" t="n">
-        <v>15998</v>
+        <v>487</v>
       </c>
       <c r="R39" s="28" t="inlineStr">
         <is>
@@ -6378,37 +6358,37 @@
         </is>
       </c>
       <c r="G40" s="22" t="n">
-        <v>21307</v>
+        <v>658</v>
       </c>
       <c r="H40" s="23" t="n">
         <v>75</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>15980</v>
+        <v>493</v>
       </c>
       <c r="J40" s="24" t="n">
         <v>22.3</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>4751</v>
+        <v>147</v>
       </c>
       <c r="L40" s="25" t="n">
         <v>1.4</v>
       </c>
       <c r="M40" s="25" t="n">
-        <v>298</v>
+        <v>9</v>
       </c>
       <c r="N40" s="26" t="n">
         <v>1.4</v>
       </c>
       <c r="O40" s="26" t="n">
-        <v>298</v>
+        <v>9</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>25.1</v>
       </c>
       <c r="Q40" s="27" t="n">
-        <v>5348</v>
+        <v>165</v>
       </c>
       <c r="R40" s="28" t="inlineStr">
         <is>
@@ -6432,37 +6412,37 @@
         </is>
       </c>
       <c r="G41" s="22" t="n">
-        <v>18071</v>
+        <v>3016</v>
       </c>
       <c r="H41" s="23" t="n">
         <v>52</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>9397</v>
+        <v>1568</v>
       </c>
       <c r="J41" s="24" t="n">
         <v>31.8</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>5747</v>
+        <v>959</v>
       </c>
       <c r="L41" s="25" t="n">
         <v>2.6</v>
       </c>
       <c r="M41" s="25" t="n">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="N41" s="26" t="n">
         <v>13.6</v>
       </c>
       <c r="O41" s="26" t="n">
-        <v>2458</v>
+        <v>410</v>
       </c>
       <c r="P41" s="27" t="n">
         <v>48</v>
       </c>
       <c r="Q41" s="27" t="n">
-        <v>8674</v>
+        <v>1448</v>
       </c>
       <c r="R41" s="28" t="inlineStr">
         <is>
@@ -6486,37 +6466,37 @@
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>6381</v>
+        <v>705</v>
       </c>
       <c r="H42" s="23" t="n">
         <v>47.9</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>3057</v>
+        <v>337</v>
       </c>
       <c r="J42" s="24" t="n">
         <v>34.5</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>2202</v>
+        <v>243</v>
       </c>
       <c r="L42" s="25" t="n">
         <v>3.6</v>
       </c>
       <c r="M42" s="25" t="n">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="N42" s="26" t="n">
         <v>13.9</v>
       </c>
       <c r="O42" s="26" t="n">
-        <v>887</v>
+        <v>98</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>52</v>
       </c>
       <c r="Q42" s="27" t="n">
-        <v>3318</v>
+        <v>366</v>
       </c>
       <c r="R42" s="28" t="inlineStr">
         <is>
@@ -6540,37 +6520,37 @@
         </is>
       </c>
       <c r="G43" s="22" t="n">
-        <v>15352</v>
+        <v>1671</v>
       </c>
       <c r="H43" s="23" t="n">
         <v>19.7</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>3024</v>
+        <v>329</v>
       </c>
       <c r="J43" s="24" t="n">
         <v>57.3</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>8797</v>
+        <v>957</v>
       </c>
       <c r="L43" s="25" t="n">
         <v>5.8</v>
       </c>
       <c r="M43" s="25" t="n">
-        <v>890</v>
+        <v>97</v>
       </c>
       <c r="N43" s="26" t="n">
         <v>17.2</v>
       </c>
       <c r="O43" s="26" t="n">
-        <v>2641</v>
+        <v>287</v>
       </c>
       <c r="P43" s="27" t="n">
         <v>80.3</v>
       </c>
       <c r="Q43" s="27" t="n">
-        <v>12328</v>
+        <v>1341</v>
       </c>
       <c r="R43" s="28" t="inlineStr">
         <is>
@@ -6594,37 +6574,37 @@
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>47891</v>
+        <v>5296</v>
       </c>
       <c r="H44" s="23" t="n">
         <v>68.7</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>32901</v>
+        <v>3638</v>
       </c>
       <c r="J44" s="24" t="n">
         <v>30.1</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>14415</v>
+        <v>1594</v>
       </c>
       <c r="L44" s="25" t="n">
         <v>0.9</v>
       </c>
       <c r="M44" s="25" t="n">
-        <v>431</v>
+        <v>48</v>
       </c>
       <c r="N44" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="O44" s="26" t="n">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>31.3</v>
       </c>
       <c r="Q44" s="27" t="n">
-        <v>14990</v>
+        <v>1658</v>
       </c>
       <c r="R44" s="28" t="inlineStr">
         <is>
@@ -6648,37 +6628,37 @@
         </is>
       </c>
       <c r="G45" s="22" t="n">
-        <v>11537</v>
+        <v>1239</v>
       </c>
       <c r="H45" s="23" t="n">
         <v>81.7</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>9425</v>
+        <v>1012</v>
       </c>
       <c r="J45" s="24" t="n">
         <v>17.2</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>1984</v>
+        <v>213</v>
       </c>
       <c r="L45" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="M45" s="25" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="N45" s="26" t="n">
         <v>0.7</v>
       </c>
       <c r="O45" s="26" t="n">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="P45" s="27" t="n">
         <v>18.3</v>
       </c>
       <c r="Q45" s="27" t="n">
-        <v>2111</v>
+        <v>227</v>
       </c>
       <c r="R45" s="28" t="inlineStr">
         <is>
@@ -6702,37 +6682,37 @@
         </is>
       </c>
       <c r="G46" s="22" t="n">
-        <v>63952</v>
+        <v>11209</v>
       </c>
       <c r="H46" s="23" t="n">
         <v>65.59999999999999</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>41952</v>
+        <v>7353</v>
       </c>
       <c r="J46" s="24" t="n">
         <v>30.5</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>19505</v>
+        <v>3419</v>
       </c>
       <c r="L46" s="25" t="n">
         <v>2</v>
       </c>
       <c r="M46" s="25" t="n">
-        <v>1279</v>
+        <v>224</v>
       </c>
       <c r="N46" s="26" t="n">
         <v>2</v>
       </c>
       <c r="O46" s="26" t="n">
-        <v>1279</v>
+        <v>224</v>
       </c>
       <c r="P46" s="27" t="n">
         <v>34.5</v>
       </c>
       <c r="Q46" s="27" t="n">
-        <v>22063</v>
+        <v>3867</v>
       </c>
       <c r="R46" s="28" t="inlineStr">
         <is>
@@ -6756,37 +6736,37 @@
         </is>
       </c>
       <c r="G47" s="22" t="n">
-        <v>34438</v>
+        <v>3668</v>
       </c>
       <c r="H47" s="23" t="n">
         <v>43.4</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>14946</v>
+        <v>1592</v>
       </c>
       <c r="J47" s="24" t="n">
         <v>40.4</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>13913</v>
+        <v>1482</v>
       </c>
       <c r="L47" s="25" t="n">
         <v>10.8</v>
       </c>
       <c r="M47" s="25" t="n">
-        <v>3719</v>
+        <v>396</v>
       </c>
       <c r="N47" s="26" t="n">
         <v>5.4</v>
       </c>
       <c r="O47" s="26" t="n">
-        <v>1860</v>
+        <v>198</v>
       </c>
       <c r="P47" s="27" t="n">
         <v>56.6</v>
       </c>
       <c r="Q47" s="27" t="n">
-        <v>19492</v>
+        <v>2076</v>
       </c>
       <c r="R47" s="28" t="inlineStr">
         <is>
@@ -6810,37 +6790,37 @@
         </is>
       </c>
       <c r="G48" s="22" t="n">
-        <v>13665</v>
+        <v>6054</v>
       </c>
       <c r="H48" s="23" t="n">
         <v>76.3</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>10427</v>
+        <v>4619</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>19.8</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>2706</v>
+        <v>1199</v>
       </c>
       <c r="L48" s="25" t="n">
         <v>2.3</v>
       </c>
       <c r="M48" s="25" t="n">
-        <v>314</v>
+        <v>139</v>
       </c>
       <c r="N48" s="26" t="n">
         <v>1.7</v>
       </c>
       <c r="O48" s="26" t="n">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="P48" s="27" t="n">
         <v>23.8</v>
       </c>
       <c r="Q48" s="27" t="n">
-        <v>3252</v>
+        <v>1441</v>
       </c>
       <c r="R48" s="28" t="inlineStr">
         <is>
@@ -6864,37 +6844,37 @@
         </is>
       </c>
       <c r="G49" s="22" t="n">
-        <v>20592</v>
+        <v>3717</v>
       </c>
       <c r="H49" s="23" t="n">
         <v>70.40000000000001</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>14497</v>
+        <v>2617</v>
       </c>
       <c r="J49" s="24" t="n">
         <v>27</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>5560</v>
+        <v>1004</v>
       </c>
       <c r="L49" s="25" t="n">
         <v>2.3</v>
       </c>
       <c r="M49" s="25" t="n">
-        <v>474</v>
+        <v>85</v>
       </c>
       <c r="N49" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="O49" s="26" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="P49" s="27" t="n">
         <v>29.6</v>
       </c>
       <c r="Q49" s="27" t="n">
-        <v>6095</v>
+        <v>1100</v>
       </c>
       <c r="R49" s="28" t="inlineStr">
         <is>
@@ -6918,37 +6898,37 @@
         </is>
       </c>
       <c r="G50" s="22" t="n">
-        <v>3264</v>
+        <v>554</v>
       </c>
       <c r="H50" s="23" t="n">
         <v>62.2</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>2030</v>
+        <v>345</v>
       </c>
       <c r="J50" s="24" t="n">
         <v>35.3</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>1152</v>
+        <v>196</v>
       </c>
       <c r="L50" s="25" t="n">
         <v>2.1</v>
       </c>
       <c r="M50" s="25" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="N50" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="O50" s="26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P50" s="27" t="n">
         <v>37.7</v>
       </c>
       <c r="Q50" s="27" t="n">
-        <v>1231</v>
+        <v>209</v>
       </c>
       <c r="R50" s="28" t="inlineStr">
         <is>
@@ -6972,37 +6952,37 @@
         </is>
       </c>
       <c r="G51" s="22" t="n">
-        <v>29664</v>
+        <v>5660</v>
       </c>
       <c r="H51" s="23" t="n">
         <v>72.5</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>21507</v>
+        <v>4104</v>
       </c>
       <c r="J51" s="24" t="n">
         <v>23.5</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>6971</v>
+        <v>1330</v>
       </c>
       <c r="L51" s="25" t="n">
         <v>3.2</v>
       </c>
       <c r="M51" s="25" t="n">
-        <v>949</v>
+        <v>181</v>
       </c>
       <c r="N51" s="26" t="n">
         <v>0.9</v>
       </c>
       <c r="O51" s="26" t="n">
-        <v>267</v>
+        <v>51</v>
       </c>
       <c r="P51" s="27" t="n">
         <v>27.6</v>
       </c>
       <c r="Q51" s="27" t="n">
-        <v>8187</v>
+        <v>1562</v>
       </c>
       <c r="R51" s="28" t="inlineStr">
         <is>
@@ -7026,37 +7006,37 @@
         </is>
       </c>
       <c r="G52" s="22" t="n">
-        <v>2157</v>
+        <v>1005</v>
       </c>
       <c r="H52" s="23" t="n">
         <v>37.6</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>811</v>
+        <v>378</v>
       </c>
       <c r="J52" s="24" t="n">
         <v>55</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>1186</v>
+        <v>553</v>
       </c>
       <c r="L52" s="25" t="n">
         <v>5.5</v>
       </c>
       <c r="M52" s="25" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="N52" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="O52" s="26" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="P52" s="27" t="n">
         <v>62.3</v>
       </c>
       <c r="Q52" s="27" t="n">
-        <v>1344</v>
+        <v>626</v>
       </c>
       <c r="R52" s="28" t="inlineStr">
         <is>
@@ -7080,37 +7060,37 @@
         </is>
       </c>
       <c r="G53" s="22" t="n">
-        <v>2010</v>
+        <v>61</v>
       </c>
       <c r="H53" s="23" t="n">
         <v>52.2</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>1049</v>
+        <v>32</v>
       </c>
       <c r="J53" s="24" t="n">
         <v>34.9</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>702</v>
+        <v>21</v>
       </c>
       <c r="L53" s="25" t="n">
         <v>5.6</v>
       </c>
       <c r="M53" s="25" t="n">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="N53" s="26" t="n">
         <v>7.3</v>
       </c>
       <c r="O53" s="26" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="P53" s="27" t="n">
         <v>47.8</v>
       </c>
       <c r="Q53" s="27" t="n">
-        <v>961</v>
+        <v>29</v>
       </c>
       <c r="R53" s="28" t="inlineStr">
         <is>
@@ -7134,25 +7114,25 @@
         </is>
       </c>
       <c r="G54" s="22" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="H54" s="23" t="n">
         <v>65</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="J54" s="24" t="n">
         <v>34.1</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="L54" s="25" t="n">
         <v>0.9</v>
       </c>
       <c r="M54" s="25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N54" s="26" t="n">
         <v>0</v>
@@ -7164,7 +7144,7 @@
         <v>35</v>
       </c>
       <c r="Q54" s="27" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="R54" s="28" t="inlineStr">
         <is>
@@ -7188,25 +7168,25 @@
         </is>
       </c>
       <c r="G55" s="22" t="n">
-        <v>14648</v>
+        <v>2485</v>
       </c>
       <c r="H55" s="23" t="n">
         <v>39.1</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>5727</v>
+        <v>972</v>
       </c>
       <c r="J55" s="24" t="n">
         <v>55.1</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>8071</v>
+        <v>1369</v>
       </c>
       <c r="L55" s="25" t="n">
         <v>5.8</v>
       </c>
       <c r="M55" s="25" t="n">
-        <v>850</v>
+        <v>144</v>
       </c>
       <c r="N55" s="26" t="n">
         <v>0</v>
@@ -7218,7 +7198,7 @@
         <v>60.9</v>
       </c>
       <c r="Q55" s="27" t="n">
-        <v>8921</v>
+        <v>1513</v>
       </c>
       <c r="R55" s="28" t="inlineStr">
         <is>
@@ -7242,25 +7222,25 @@
         </is>
       </c>
       <c r="G56" s="22" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H56" s="23" t="n">
         <v>72.2</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J56" s="24" t="n">
         <v>23.1</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L56" s="25" t="n">
         <v>4.7</v>
       </c>
       <c r="M56" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N56" s="26" t="n">
         <v>0</v>
@@ -7272,7 +7252,7 @@
         <v>27.8</v>
       </c>
       <c r="Q56" s="27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R56" s="28" t="inlineStr">
         <is>
@@ -7296,37 +7276,37 @@
         </is>
       </c>
       <c r="G57" s="22" t="n">
-        <v>26644</v>
+        <v>2819</v>
       </c>
       <c r="H57" s="23" t="n">
         <v>69.3</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>18465</v>
+        <v>1953</v>
       </c>
       <c r="J57" s="24" t="n">
         <v>29.6</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>7887</v>
+        <v>834</v>
       </c>
       <c r="L57" s="25" t="n">
         <v>0.8</v>
       </c>
       <c r="M57" s="25" t="n">
-        <v>213</v>
+        <v>23</v>
       </c>
       <c r="N57" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="O57" s="26" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="P57" s="27" t="n">
         <v>30.7</v>
       </c>
       <c r="Q57" s="27" t="n">
-        <v>8180</v>
+        <v>865</v>
       </c>
       <c r="R57" s="28" t="inlineStr">
         <is>
@@ -7350,37 +7330,37 @@
         </is>
       </c>
       <c r="G58" s="22" t="n">
-        <v>38219</v>
+        <v>6458</v>
       </c>
       <c r="H58" s="23" t="n">
         <v>54.2</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>20714</v>
+        <v>3500</v>
       </c>
       <c r="J58" s="24" t="n">
         <v>37.4</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>14294</v>
+        <v>2415</v>
       </c>
       <c r="L58" s="25" t="n">
         <v>3.5</v>
       </c>
       <c r="M58" s="25" t="n">
-        <v>1338</v>
+        <v>226</v>
       </c>
       <c r="N58" s="26" t="n">
         <v>4.9</v>
       </c>
       <c r="O58" s="26" t="n">
-        <v>1873</v>
+        <v>316</v>
       </c>
       <c r="P58" s="27" t="n">
         <v>45.8</v>
       </c>
       <c r="Q58" s="27" t="n">
-        <v>17504</v>
+        <v>2958</v>
       </c>
       <c r="R58" s="28" t="inlineStr">
         <is>
@@ -7404,25 +7384,25 @@
         </is>
       </c>
       <c r="G59" s="22" t="n">
-        <v>13138</v>
+        <v>2629</v>
       </c>
       <c r="H59" s="23" t="n">
         <v>47.2</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>6201</v>
+        <v>1241</v>
       </c>
       <c r="J59" s="24" t="n">
         <v>48.9</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>6425</v>
+        <v>1286</v>
       </c>
       <c r="L59" s="25" t="n">
         <v>3.9</v>
       </c>
       <c r="M59" s="25" t="n">
-        <v>512</v>
+        <v>103</v>
       </c>
       <c r="N59" s="26" t="n">
         <v>0</v>
@@ -7434,7 +7414,7 @@
         <v>52.8</v>
       </c>
       <c r="Q59" s="27" t="n">
-        <v>6937</v>
+        <v>1388</v>
       </c>
       <c r="R59" s="28" t="inlineStr">
         <is>
@@ -7458,37 +7438,37 @@
         </is>
       </c>
       <c r="G60" s="22" t="n">
-        <v>12639</v>
+        <v>389</v>
       </c>
       <c r="H60" s="23" t="n">
         <v>49.8</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>6294</v>
+        <v>194</v>
       </c>
       <c r="J60" s="24" t="n">
         <v>46.8</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>5915</v>
+        <v>182</v>
       </c>
       <c r="L60" s="25" t="n">
         <v>1.8</v>
       </c>
       <c r="M60" s="25" t="n">
-        <v>227</v>
+        <v>7</v>
       </c>
       <c r="N60" s="26" t="n">
         <v>1.5</v>
       </c>
       <c r="O60" s="26" t="n">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="P60" s="27" t="n">
         <v>50.1</v>
       </c>
       <c r="Q60" s="27" t="n">
-        <v>6332</v>
+        <v>195</v>
       </c>
       <c r="R60" s="28" t="inlineStr">
         <is>
@@ -7512,37 +7492,37 @@
         </is>
       </c>
       <c r="G61" s="22" t="n">
-        <v>37799</v>
+        <v>1154</v>
       </c>
       <c r="H61" s="23" t="n">
         <v>68.2</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>25779</v>
+        <v>787</v>
       </c>
       <c r="J61" s="24" t="n">
         <v>28.6</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>10811</v>
+        <v>330</v>
       </c>
       <c r="L61" s="25" t="n">
         <v>2.4</v>
       </c>
       <c r="M61" s="25" t="n">
-        <v>907</v>
+        <v>28</v>
       </c>
       <c r="N61" s="26" t="n">
         <v>0.8</v>
       </c>
       <c r="O61" s="26" t="n">
-        <v>302</v>
+        <v>9</v>
       </c>
       <c r="P61" s="27" t="n">
         <v>31.8</v>
       </c>
       <c r="Q61" s="27" t="n">
-        <v>12020</v>
+        <v>367</v>
       </c>
       <c r="R61" s="28" t="inlineStr">
         <is>
@@ -7566,37 +7546,37 @@
         </is>
       </c>
       <c r="G62" s="22" t="n">
-        <v>10820</v>
+        <v>566</v>
       </c>
       <c r="H62" s="23" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>3246</v>
+        <v>170</v>
       </c>
       <c r="J62" s="24" t="n">
         <v>61.3</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>6633</v>
+        <v>347</v>
       </c>
       <c r="L62" s="25" t="n">
         <v>4.6</v>
       </c>
       <c r="M62" s="25" t="n">
-        <v>498</v>
+        <v>26</v>
       </c>
       <c r="N62" s="26" t="n">
         <v>4.1</v>
       </c>
       <c r="O62" s="26" t="n">
-        <v>444</v>
+        <v>23</v>
       </c>
       <c r="P62" s="27" t="n">
         <v>70</v>
       </c>
       <c r="Q62" s="27" t="n">
-        <v>7574</v>
+        <v>396</v>
       </c>
       <c r="R62" s="28" t="inlineStr">
         <is>
@@ -7620,37 +7600,37 @@
         </is>
       </c>
       <c r="G63" s="22" t="n">
-        <v>4940</v>
+        <v>2317</v>
       </c>
       <c r="H63" s="23" t="n">
         <v>70.3</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>3473</v>
+        <v>1629</v>
       </c>
       <c r="J63" s="24" t="n">
         <v>25.5</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>1260</v>
+        <v>591</v>
       </c>
       <c r="L63" s="25" t="n">
         <v>1.7</v>
       </c>
       <c r="M63" s="25" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="N63" s="26" t="n">
         <v>2.4</v>
       </c>
       <c r="O63" s="26" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="P63" s="27" t="n">
         <v>29.6</v>
       </c>
       <c r="Q63" s="27" t="n">
-        <v>1462</v>
+        <v>686</v>
       </c>
       <c r="R63" s="28" t="inlineStr">
         <is>
@@ -7674,37 +7654,37 @@
         </is>
       </c>
       <c r="G64" s="22" t="n">
-        <v>5954</v>
+        <v>2994</v>
       </c>
       <c r="H64" s="23" t="n">
         <v>54.1</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>3221</v>
+        <v>1620</v>
       </c>
       <c r="J64" s="24" t="n">
         <v>39.8</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>2370</v>
+        <v>1192</v>
       </c>
       <c r="L64" s="25" t="n">
         <v>4.1</v>
       </c>
       <c r="M64" s="25" t="n">
-        <v>244</v>
+        <v>123</v>
       </c>
       <c r="N64" s="26" t="n">
         <v>2</v>
       </c>
       <c r="O64" s="26" t="n">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="P64" s="27" t="n">
         <v>45.9</v>
       </c>
       <c r="Q64" s="27" t="n">
-        <v>2733</v>
+        <v>1374</v>
       </c>
       <c r="R64" s="28" t="inlineStr">
         <is>
@@ -7728,37 +7708,37 @@
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>7687</v>
+        <v>1607</v>
       </c>
       <c r="H65" s="23" t="n">
         <v>31.5</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>2421</v>
+        <v>506</v>
       </c>
       <c r="J65" s="24" t="n">
         <v>33.7</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>2591</v>
+        <v>541</v>
       </c>
       <c r="L65" s="25" t="n">
         <v>3.4</v>
       </c>
       <c r="M65" s="25" t="n">
-        <v>261</v>
+        <v>55</v>
       </c>
       <c r="N65" s="26" t="n">
         <v>31.5</v>
       </c>
       <c r="O65" s="26" t="n">
-        <v>2421</v>
+        <v>506</v>
       </c>
       <c r="P65" s="27" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="Q65" s="27" t="n">
-        <v>5273</v>
+        <v>1102</v>
       </c>
       <c r="R65" s="28" t="inlineStr">
         <is>
@@ -7782,37 +7762,37 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="H66" s="23" t="n">
         <v>27.7</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="J66" s="24" t="n">
         <v>50.6</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="L66" s="25" t="n">
         <v>14.5</v>
       </c>
       <c r="M66" s="25" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N66" s="26" t="n">
         <v>7.2</v>
       </c>
       <c r="O66" s="26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="P66" s="27" t="n">
         <v>72.3</v>
       </c>
       <c r="Q66" s="27" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="R66" s="28" t="inlineStr">
         <is>
@@ -7836,37 +7816,37 @@
         </is>
       </c>
       <c r="G67" s="29" t="n">
-        <v>163575</v>
+        <v>18069</v>
       </c>
       <c r="H67" s="30" t="n">
         <v>61.5</v>
       </c>
       <c r="I67" s="30" t="n">
-        <v>100599</v>
+        <v>11112</v>
       </c>
       <c r="J67" s="31" t="n">
         <v>36.3</v>
       </c>
       <c r="K67" s="31" t="n">
-        <v>59378</v>
+        <v>6559</v>
       </c>
       <c r="L67" s="32" t="n">
         <v>0.4</v>
       </c>
       <c r="M67" s="32" t="n">
-        <v>654</v>
+        <v>72</v>
       </c>
       <c r="N67" s="33" t="n">
         <v>1.8</v>
       </c>
       <c r="O67" s="33" t="n">
-        <v>2944</v>
+        <v>325</v>
       </c>
       <c r="P67" s="34" t="n">
         <v>38.5</v>
       </c>
       <c r="Q67" s="34" t="n">
-        <v>62976</v>
+        <v>6957</v>
       </c>
       <c r="R67" s="28" t="inlineStr">
         <is>
